--- a/h100price/static/exports/b300_rental_prices.xlsx
+++ b/h100price/static/exports/b300_rental_prices.xlsx
@@ -18518,6 +18518,8812 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G251">
+        <v>7.339259</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J251">
+        <v>1</v>
+      </c>
+      <c r="K251">
+        <v>7.339259</v>
+      </c>
+      <c r="L251">
+        <v>7.339259</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9645921,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G252">
+        <v>14.672593</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J252">
+        <v>2</v>
+      </c>
+      <c r="K252">
+        <v>7.336296</v>
+      </c>
+      <c r="L252">
+        <v>7.336296</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9645921,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G253">
+        <v>18.671111</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J253">
+        <v>2</v>
+      </c>
+      <c r="K253">
+        <v>9.335556</v>
+      </c>
+      <c r="L253">
+        <v>9.335556</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9837279,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G254">
+        <v>29.334815</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J254">
+        <v>4</v>
+      </c>
+      <c r="K254">
+        <v>7.333704</v>
+      </c>
+      <c r="L254">
+        <v>7.333704</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404991,"reliability":0.9020099,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G255">
+        <v>37.237037</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J255">
+        <v>4</v>
+      </c>
+      <c r="K255">
+        <v>9.309259</v>
+      </c>
+      <c r="L255">
+        <v>9.309259</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260728,"reliability":0.9243507,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G256">
+        <v>37.334815</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J256">
+        <v>4</v>
+      </c>
+      <c r="K256">
+        <v>9.333704</v>
+      </c>
+      <c r="L256">
+        <v>9.333704</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8682669,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G257">
+        <v>58.668148</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J257">
+        <v>8</v>
+      </c>
+      <c r="K257">
+        <v>7.333519</v>
+      </c>
+      <c r="L257">
+        <v>7.333519</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154050,"reliability":0.9643686,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G258">
+        <v>74.463704</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J258">
+        <v>8</v>
+      </c>
+      <c r="K258">
+        <v>9.307963</v>
+      </c>
+      <c r="L258">
+        <v>9.307963</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260727,"reliability":0.9243507,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G259">
+        <v>74.668148</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J259">
+        <v>8</v>
+      </c>
+      <c r="K259">
+        <v>9.333519</v>
+      </c>
+      <c r="L259">
+        <v>9.333519</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8682669,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G260">
+        <v>7.339259</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J260">
+        <v>1</v>
+      </c>
+      <c r="K260">
+        <v>7.339259</v>
+      </c>
+      <c r="L260">
+        <v>7.339259</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404972,"reliability":0.9651111,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G261">
+        <v>14.668148</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J261">
+        <v>2</v>
+      </c>
+      <c r="K261">
+        <v>7.334074</v>
+      </c>
+      <c r="L261">
+        <v>7.334074</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9649963,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G262">
+        <v>18.671111</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J262">
+        <v>2</v>
+      </c>
+      <c r="K262">
+        <v>9.335556</v>
+      </c>
+      <c r="L262">
+        <v>9.335556</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9837972,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G263">
+        <v>29.334815</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J263">
+        <v>4</v>
+      </c>
+      <c r="K263">
+        <v>7.333704</v>
+      </c>
+      <c r="L263">
+        <v>7.333704</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154039,"reliability":0.9649963,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G264">
+        <v>37.237037</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J264">
+        <v>4</v>
+      </c>
+      <c r="K264">
+        <v>9.309259</v>
+      </c>
+      <c r="L264">
+        <v>9.309259</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260728,"reliability":0.92532,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G265">
+        <v>37.334815</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J265">
+        <v>4</v>
+      </c>
+      <c r="K265">
+        <v>9.333704</v>
+      </c>
+      <c r="L265">
+        <v>9.333704</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8727415,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G266">
+        <v>56.001481</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J266">
+        <v>8</v>
+      </c>
+      <c r="K266">
+        <v>7.000185</v>
+      </c>
+      <c r="L266">
+        <v>7.000185</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38268067,"reliability":0.9543217,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G267">
+        <v>74.463704</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J267">
+        <v>8</v>
+      </c>
+      <c r="K267">
+        <v>9.307963</v>
+      </c>
+      <c r="L267">
+        <v>9.307963</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260727,"reliability":0.92532,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G268">
+        <v>74.668148</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J268">
+        <v>8</v>
+      </c>
+      <c r="K268">
+        <v>9.333519</v>
+      </c>
+      <c r="L268">
+        <v>9.333519</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8727415,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G269">
+        <v>7.334815</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269">
+        <v>7.334815</v>
+      </c>
+      <c r="L269">
+        <v>7.334815</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154051,"reliability":0.9652959,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G270">
+        <v>14.668148</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J270">
+        <v>2</v>
+      </c>
+      <c r="K270">
+        <v>7.334074</v>
+      </c>
+      <c r="L270">
+        <v>7.334074</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404988,"reliability":0.9134983,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G271">
+        <v>18.671111</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J271">
+        <v>2</v>
+      </c>
+      <c r="K271">
+        <v>9.335556</v>
+      </c>
+      <c r="L271">
+        <v>9.335556</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9838746,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G272">
+        <v>29.334815</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J272">
+        <v>4</v>
+      </c>
+      <c r="K272">
+        <v>7.333704</v>
+      </c>
+      <c r="L272">
+        <v>7.333704</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154048,"reliability":0.9652959,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G273">
+        <v>37.237037</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J273">
+        <v>4</v>
+      </c>
+      <c r="K273">
+        <v>9.309259</v>
+      </c>
+      <c r="L273">
+        <v>9.309259</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260728,"reliability":0.9263628,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G274">
+        <v>37.334815</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J274">
+        <v>4</v>
+      </c>
+      <c r="K274">
+        <v>9.333704</v>
+      </c>
+      <c r="L274">
+        <v>9.333704</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.877215,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G275">
+        <v>58.668148</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J275">
+        <v>8</v>
+      </c>
+      <c r="K275">
+        <v>7.333519</v>
+      </c>
+      <c r="L275">
+        <v>7.333519</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154050,"reliability":0.9652959,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G276">
+        <v>74.463704</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J276">
+        <v>8</v>
+      </c>
+      <c r="K276">
+        <v>9.307963</v>
+      </c>
+      <c r="L276">
+        <v>9.307963</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260727,"reliability":0.9263628,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G277">
+        <v>74.668148</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J277">
+        <v>8</v>
+      </c>
+      <c r="K277">
+        <v>9.333519</v>
+      </c>
+      <c r="L277">
+        <v>9.333519</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.877215,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G278">
+        <v>7.339259</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278">
+        <v>7.339259</v>
+      </c>
+      <c r="L278">
+        <v>7.339259</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.965183,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G279">
+        <v>14.668148</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J279">
+        <v>2</v>
+      </c>
+      <c r="K279">
+        <v>7.334074</v>
+      </c>
+      <c r="L279">
+        <v>7.334074</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154046,"reliability":0.9654443,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G280">
+        <v>17.21037</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J280">
+        <v>2</v>
+      </c>
+      <c r="K280">
+        <v>8.605185</v>
+      </c>
+      <c r="L280">
+        <v>8.605185</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456456,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G281">
+        <v>18.671111</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J281">
+        <v>2</v>
+      </c>
+      <c r="K281">
+        <v>9.335556</v>
+      </c>
+      <c r="L281">
+        <v>9.335556</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9839488,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G282">
+        <v>32.001481</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J282">
+        <v>4</v>
+      </c>
+      <c r="K282">
+        <v>8.00037</v>
+      </c>
+      <c r="L282">
+        <v>8.00037</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404991,"reliability":0.9151004,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G283">
+        <v>34.41037</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J283">
+        <v>4</v>
+      </c>
+      <c r="K283">
+        <v>8.602593</v>
+      </c>
+      <c r="L283">
+        <v>8.602593</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456453,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G284">
+        <v>37.334815</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J284">
+        <v>4</v>
+      </c>
+      <c r="K284">
+        <v>9.333704</v>
+      </c>
+      <c r="L284">
+        <v>9.333704</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.8811544,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G285">
+        <v>64.001481</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J285">
+        <v>8</v>
+      </c>
+      <c r="K285">
+        <v>8.000185</v>
+      </c>
+      <c r="L285">
+        <v>8.000185</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404992,"reliability":0.9151004,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G286">
+        <v>68.81037</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J286">
+        <v>8</v>
+      </c>
+      <c r="K286">
+        <v>8.601296</v>
+      </c>
+      <c r="L286">
+        <v>8.601296</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456458,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G287">
+        <v>74.668148</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J287">
+        <v>8</v>
+      </c>
+      <c r="K287">
+        <v>9.333519</v>
+      </c>
+      <c r="L287">
+        <v>9.333519</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8811544,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G288">
+        <v>7.334815</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J288">
+        <v>1</v>
+      </c>
+      <c r="K288">
+        <v>7.334815</v>
+      </c>
+      <c r="L288">
+        <v>7.334815</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154051,"reliability":0.9654443,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G289">
+        <v>14.668148</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J289">
+        <v>2</v>
+      </c>
+      <c r="K289">
+        <v>7.334074</v>
+      </c>
+      <c r="L289">
+        <v>7.334074</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9654443,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G290">
+        <v>17.21037</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J290">
+        <v>2</v>
+      </c>
+      <c r="K290">
+        <v>8.605185</v>
+      </c>
+      <c r="L290">
+        <v>8.605185</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456455,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G291">
+        <v>18.671111</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J291">
+        <v>2</v>
+      </c>
+      <c r="K291">
+        <v>9.335556</v>
+      </c>
+      <c r="L291">
+        <v>9.335556</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9839488,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G292">
+        <v>32.001481</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J292">
+        <v>4</v>
+      </c>
+      <c r="K292">
+        <v>8.00037</v>
+      </c>
+      <c r="L292">
+        <v>8.00037</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404987,"reliability":0.9151004,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G293">
+        <v>34.41037</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J293">
+        <v>4</v>
+      </c>
+      <c r="K293">
+        <v>8.602593</v>
+      </c>
+      <c r="L293">
+        <v>8.602593</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456457,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G294">
+        <v>37.334815</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J294">
+        <v>4</v>
+      </c>
+      <c r="K294">
+        <v>9.333704</v>
+      </c>
+      <c r="L294">
+        <v>9.333704</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8811544,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G295">
+        <v>64.001481</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J295">
+        <v>8</v>
+      </c>
+      <c r="K295">
+        <v>8.000185</v>
+      </c>
+      <c r="L295">
+        <v>8.000185</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404992,"reliability":0.9151004,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G296">
+        <v>68.81037</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J296">
+        <v>8</v>
+      </c>
+      <c r="K296">
+        <v>8.601296</v>
+      </c>
+      <c r="L296">
+        <v>8.601296</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456458,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G297">
+        <v>74.668148</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J297">
+        <v>8</v>
+      </c>
+      <c r="K297">
+        <v>9.333519</v>
+      </c>
+      <c r="L297">
+        <v>9.333519</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8811544,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G298">
+        <v>7.339259</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J298">
+        <v>1</v>
+      </c>
+      <c r="K298">
+        <v>7.339259</v>
+      </c>
+      <c r="L298">
+        <v>7.339259</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9653552,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G299">
+        <v>9.335556</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J299">
+        <v>1</v>
+      </c>
+      <c r="K299">
+        <v>9.335556</v>
+      </c>
+      <c r="L299">
+        <v>9.335556</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345039,"reliability":0.9639402,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G300">
+        <v>14.668148</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J300">
+        <v>2</v>
+      </c>
+      <c r="K300">
+        <v>7.334074</v>
+      </c>
+      <c r="L300">
+        <v>7.334074</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9655646,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G301">
+        <v>17.21037</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J301">
+        <v>2</v>
+      </c>
+      <c r="K301">
+        <v>8.605185</v>
+      </c>
+      <c r="L301">
+        <v>8.605185</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456454,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G302">
+        <v>18.668889</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J302">
+        <v>2</v>
+      </c>
+      <c r="K302">
+        <v>9.334444</v>
+      </c>
+      <c r="L302">
+        <v>9.334444</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345026,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G303">
+        <v>18.671111</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J303">
+        <v>2</v>
+      </c>
+      <c r="K303">
+        <v>9.335556</v>
+      </c>
+      <c r="L303">
+        <v>9.335556</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9842316,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G304">
+        <v>29.334815</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J304">
+        <v>4</v>
+      </c>
+      <c r="K304">
+        <v>7.333704</v>
+      </c>
+      <c r="L304">
+        <v>7.333704</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154048,"reliability":0.9655646,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G305">
+        <v>34.41037</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J305">
+        <v>4</v>
+      </c>
+      <c r="K305">
+        <v>8.602593</v>
+      </c>
+      <c r="L305">
+        <v>8.602593</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456457,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G306">
+        <v>37.334815</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J306">
+        <v>4</v>
+      </c>
+      <c r="K306">
+        <v>9.333704</v>
+      </c>
+      <c r="L306">
+        <v>9.333704</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8939438,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G307">
+        <v>37.335556</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J307">
+        <v>4</v>
+      </c>
+      <c r="K307">
+        <v>9.333889</v>
+      </c>
+      <c r="L307">
+        <v>9.333889</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345023,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G308">
+        <v>61.334815</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J308">
+        <v>8</v>
+      </c>
+      <c r="K308">
+        <v>7.666852</v>
+      </c>
+      <c r="L308">
+        <v>7.666852</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38268067,"reliability":0.9551375,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G309">
+        <v>64.002222</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J309">
+        <v>8</v>
+      </c>
+      <c r="K309">
+        <v>8.000278</v>
+      </c>
+      <c r="L309">
+        <v>8.000278</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9599371,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G310">
+        <v>68.81037</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J310">
+        <v>8</v>
+      </c>
+      <c r="K310">
+        <v>8.601296</v>
+      </c>
+      <c r="L310">
+        <v>8.601296</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456458,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G311">
+        <v>74.668148</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J311">
+        <v>8</v>
+      </c>
+      <c r="K311">
+        <v>9.333519</v>
+      </c>
+      <c r="L311">
+        <v>9.333519</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8939438,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G312">
+        <v>74.668889</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J312">
+        <v>8</v>
+      </c>
+      <c r="K312">
+        <v>9.333611</v>
+      </c>
+      <c r="L312">
+        <v>9.333611</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G313">
+        <v>7.339259</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J313">
+        <v>1</v>
+      </c>
+      <c r="K313">
+        <v>7.339259</v>
+      </c>
+      <c r="L313">
+        <v>7.339259</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9653552,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G314">
+        <v>9.335556</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J314">
+        <v>1</v>
+      </c>
+      <c r="K314">
+        <v>9.335556</v>
+      </c>
+      <c r="L314">
+        <v>9.335556</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345020,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G315">
+        <v>14.668148</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J315">
+        <v>2</v>
+      </c>
+      <c r="K315">
+        <v>7.334074</v>
+      </c>
+      <c r="L315">
+        <v>7.334074</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154037,"reliability":0.9655646,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G316">
+        <v>17.21037</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J316">
+        <v>2</v>
+      </c>
+      <c r="K316">
+        <v>8.605185</v>
+      </c>
+      <c r="L316">
+        <v>8.605185</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456456,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G317">
+        <v>18.668889</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J317">
+        <v>2</v>
+      </c>
+      <c r="K317">
+        <v>9.334444</v>
+      </c>
+      <c r="L317">
+        <v>9.334444</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345021,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G318">
+        <v>18.671111</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J318">
+        <v>2</v>
+      </c>
+      <c r="K318">
+        <v>9.335556</v>
+      </c>
+      <c r="L318">
+        <v>9.335556</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9842316,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G319">
+        <v>29.334815</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J319">
+        <v>4</v>
+      </c>
+      <c r="K319">
+        <v>7.333704</v>
+      </c>
+      <c r="L319">
+        <v>7.333704</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154048,"reliability":0.9655646,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G320">
+        <v>34.41037</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J320">
+        <v>4</v>
+      </c>
+      <c r="K320">
+        <v>8.602593</v>
+      </c>
+      <c r="L320">
+        <v>8.602593</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456453,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G321">
+        <v>37.334815</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J321">
+        <v>4</v>
+      </c>
+      <c r="K321">
+        <v>9.333704</v>
+      </c>
+      <c r="L321">
+        <v>9.333704</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.8939438,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G322">
+        <v>37.335556</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J322">
+        <v>4</v>
+      </c>
+      <c r="K322">
+        <v>9.333889</v>
+      </c>
+      <c r="L322">
+        <v>9.333889</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345051,"reliability":0.9639402,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G323">
+        <v>61.334815</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J323">
+        <v>8</v>
+      </c>
+      <c r="K323">
+        <v>7.666852</v>
+      </c>
+      <c r="L323">
+        <v>7.666852</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38268067,"reliability":0.9551375,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G324">
+        <v>64.002222</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J324">
+        <v>8</v>
+      </c>
+      <c r="K324">
+        <v>8.000278</v>
+      </c>
+      <c r="L324">
+        <v>8.000278</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9599371,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G325">
+        <v>68.81037</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J325">
+        <v>8</v>
+      </c>
+      <c r="K325">
+        <v>8.601296</v>
+      </c>
+      <c r="L325">
+        <v>8.601296</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456458,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G326">
+        <v>74.668148</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J326">
+        <v>8</v>
+      </c>
+      <c r="K326">
+        <v>9.333519</v>
+      </c>
+      <c r="L326">
+        <v>9.333519</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8939438,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G327">
+        <v>74.668889</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J327">
+        <v>8</v>
+      </c>
+      <c r="K327">
+        <v>9.333611</v>
+      </c>
+      <c r="L327">
+        <v>9.333611</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G328">
+        <v>8.005926</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J328">
+        <v>1</v>
+      </c>
+      <c r="K328">
+        <v>8.005926</v>
+      </c>
+      <c r="L328">
+        <v>8.005926</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9654368,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G329">
+        <v>9.335556</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329">
+        <v>9.335556</v>
+      </c>
+      <c r="L329">
+        <v>9.335556</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345043,"reliability":0.9639918,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G330">
+        <v>9.335556</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330">
+        <v>9.335556</v>
+      </c>
+      <c r="L330">
+        <v>9.335556</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345024,"reliability":0.9639771,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G331">
+        <v>10.668148</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331">
+        <v>10.668148</v>
+      </c>
+      <c r="L331">
+        <v>10.668148</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487071,"reliability":0.900017,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G332">
+        <v>16.001481</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J332">
+        <v>2</v>
+      </c>
+      <c r="K332">
+        <v>8.000741</v>
+      </c>
+      <c r="L332">
+        <v>8.000741</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9656243,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G333">
+        <v>17.21037</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J333">
+        <v>2</v>
+      </c>
+      <c r="K333">
+        <v>8.605185</v>
+      </c>
+      <c r="L333">
+        <v>8.605185</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456455,"reliability":0.9322829,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G334">
+        <v>18.668889</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J334">
+        <v>2</v>
+      </c>
+      <c r="K334">
+        <v>9.334444</v>
+      </c>
+      <c r="L334">
+        <v>9.334444</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345044,"reliability":0.9639918,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G335">
+        <v>18.668889</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J335">
+        <v>2</v>
+      </c>
+      <c r="K335">
+        <v>9.334444</v>
+      </c>
+      <c r="L335">
+        <v>9.334444</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9639771,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G336">
+        <v>21.334815</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J336">
+        <v>2</v>
+      </c>
+      <c r="K336">
+        <v>10.667407</v>
+      </c>
+      <c r="L336">
+        <v>10.667407</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487075,"reliability":0.900017,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G337">
+        <v>32.001481</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J337">
+        <v>4</v>
+      </c>
+      <c r="K337">
+        <v>8.00037</v>
+      </c>
+      <c r="L337">
+        <v>8.00037</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154039,"reliability":0.9656243,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G338">
+        <v>34.41037</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J338">
+        <v>4</v>
+      </c>
+      <c r="K338">
+        <v>8.602593</v>
+      </c>
+      <c r="L338">
+        <v>8.602593</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456453,"reliability":0.9322829,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G339">
+        <v>37.334815</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J339">
+        <v>4</v>
+      </c>
+      <c r="K339">
+        <v>9.333704</v>
+      </c>
+      <c r="L339">
+        <v>9.333704</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.8990529,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G340">
+        <v>37.335556</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J340">
+        <v>4</v>
+      </c>
+      <c r="K340">
+        <v>9.333889</v>
+      </c>
+      <c r="L340">
+        <v>9.333889</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345032,"reliability":0.9639771,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G341">
+        <v>37.335556</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J341">
+        <v>4</v>
+      </c>
+      <c r="K341">
+        <v>9.333889</v>
+      </c>
+      <c r="L341">
+        <v>9.333889</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345051,"reliability":0.9639918,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G342">
+        <v>42.668148</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J342">
+        <v>4</v>
+      </c>
+      <c r="K342">
+        <v>10.667037</v>
+      </c>
+      <c r="L342">
+        <v>10.667037</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487081,"reliability":0.900017,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G343">
+        <v>64.002222</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J343">
+        <v>8</v>
+      </c>
+      <c r="K343">
+        <v>8.000278</v>
+      </c>
+      <c r="L343">
+        <v>8.000278</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9600876,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G344">
+        <v>74.668148</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J344">
+        <v>8</v>
+      </c>
+      <c r="K344">
+        <v>9.333519</v>
+      </c>
+      <c r="L344">
+        <v>9.333519</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8990529,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G345">
+        <v>74.668889</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J345">
+        <v>8</v>
+      </c>
+      <c r="K345">
+        <v>9.333611</v>
+      </c>
+      <c r="L345">
+        <v>9.333611</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345052,"reliability":0.9639918,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G346">
+        <v>74.668889</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J346">
+        <v>8</v>
+      </c>
+      <c r="K346">
+        <v>9.333611</v>
+      </c>
+      <c r="L346">
+        <v>9.333611</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9639771,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G347">
+        <v>85.334815</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J347">
+        <v>8</v>
+      </c>
+      <c r="K347">
+        <v>10.666852</v>
+      </c>
+      <c r="L347">
+        <v>10.666852</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487082,"reliability":0.900017,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>20260530T025917Z</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:18Z</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G348">
+        <v>85.334815</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J348">
+        <v>8</v>
+      </c>
+      <c r="K348">
+        <v>10.666852</v>
+      </c>
+      <c r="L348">
+        <v>10.666852</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38268067,"reliability":0.9554946,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G349">
+        <v>8.001481</v>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J349">
+        <v>1</v>
+      </c>
+      <c r="K349">
+        <v>8.001481</v>
+      </c>
+      <c r="L349">
+        <v>8.001481</v>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154043,"reliability":0.9656243,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G350">
+        <v>9.335556</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J350">
+        <v>1</v>
+      </c>
+      <c r="K350">
+        <v>9.335556</v>
+      </c>
+      <c r="L350">
+        <v>9.335556</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345050,"reliability":0.9639918,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G351">
+        <v>9.335556</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J351">
+        <v>1</v>
+      </c>
+      <c r="K351">
+        <v>9.335556</v>
+      </c>
+      <c r="L351">
+        <v>9.335556</v>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345028,"reliability":0.9639771,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G352">
+        <v>10.668148</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J352">
+        <v>1</v>
+      </c>
+      <c r="K352">
+        <v>10.668148</v>
+      </c>
+      <c r="L352">
+        <v>10.668148</v>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487071,"reliability":0.900017,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G353">
+        <v>16.001481</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J353">
+        <v>2</v>
+      </c>
+      <c r="K353">
+        <v>8.000741</v>
+      </c>
+      <c r="L353">
+        <v>8.000741</v>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154046,"reliability":0.9656243,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G354">
+        <v>17.21037</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J354">
+        <v>2</v>
+      </c>
+      <c r="K354">
+        <v>8.605185</v>
+      </c>
+      <c r="L354">
+        <v>8.605185</v>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456455,"reliability":0.9322829,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G355">
+        <v>18.668889</v>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J355">
+        <v>2</v>
+      </c>
+      <c r="K355">
+        <v>9.334444</v>
+      </c>
+      <c r="L355">
+        <v>9.334444</v>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345044,"reliability":0.9639918,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G356">
+        <v>18.671111</v>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J356">
+        <v>2</v>
+      </c>
+      <c r="K356">
+        <v>9.335556</v>
+      </c>
+      <c r="L356">
+        <v>9.335556</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9843688,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G357">
+        <v>21.334815</v>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J357">
+        <v>2</v>
+      </c>
+      <c r="K357">
+        <v>10.667407</v>
+      </c>
+      <c r="L357">
+        <v>10.667407</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487079,"reliability":0.900017,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G358">
+        <v>32.001481</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J358">
+        <v>4</v>
+      </c>
+      <c r="K358">
+        <v>8.00037</v>
+      </c>
+      <c r="L358">
+        <v>8.00037</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154039,"reliability":0.9656243,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G359">
+        <v>34.41037</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J359">
+        <v>4</v>
+      </c>
+      <c r="K359">
+        <v>8.602593</v>
+      </c>
+      <c r="L359">
+        <v>8.602593</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456453,"reliability":0.9322829,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G360">
+        <v>37.334815</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J360">
+        <v>4</v>
+      </c>
+      <c r="K360">
+        <v>9.333704</v>
+      </c>
+      <c r="L360">
+        <v>9.333704</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8990529,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G361">
+        <v>37.335556</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J361">
+        <v>4</v>
+      </c>
+      <c r="K361">
+        <v>9.333889</v>
+      </c>
+      <c r="L361">
+        <v>9.333889</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345023,"reliability":0.9639771,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G362">
+        <v>37.335556</v>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J362">
+        <v>4</v>
+      </c>
+      <c r="K362">
+        <v>9.333889</v>
+      </c>
+      <c r="L362">
+        <v>9.333889</v>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345042,"reliability":0.9639918,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G363">
+        <v>42.668148</v>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J363">
+        <v>4</v>
+      </c>
+      <c r="K363">
+        <v>10.667037</v>
+      </c>
+      <c r="L363">
+        <v>10.667037</v>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487072,"reliability":0.900017,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G364">
+        <v>64.002222</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J364">
+        <v>8</v>
+      </c>
+      <c r="K364">
+        <v>8.000278</v>
+      </c>
+      <c r="L364">
+        <v>8.000278</v>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9600876,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G365">
+        <v>74.668148</v>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J365">
+        <v>8</v>
+      </c>
+      <c r="K365">
+        <v>9.333519</v>
+      </c>
+      <c r="L365">
+        <v>9.333519</v>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8990529,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G366">
+        <v>74.668889</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J366">
+        <v>8</v>
+      </c>
+      <c r="K366">
+        <v>9.333611</v>
+      </c>
+      <c r="L366">
+        <v>9.333611</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345052,"reliability":0.9639918,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G367">
+        <v>74.668889</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J367">
+        <v>8</v>
+      </c>
+      <c r="K367">
+        <v>9.333611</v>
+      </c>
+      <c r="L367">
+        <v>9.333611</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9639771,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G368">
+        <v>85.334815</v>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J368">
+        <v>8</v>
+      </c>
+      <c r="K368">
+        <v>10.666852</v>
+      </c>
+      <c r="L368">
+        <v>10.666852</v>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487082,"reliability":0.900017,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>20260530T025959Z</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026-05-30T03:00:01Z</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G369">
+        <v>85.334815</v>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J369">
+        <v>8</v>
+      </c>
+      <c r="K369">
+        <v>10.666852</v>
+      </c>
+      <c r="L369">
+        <v>10.666852</v>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38268067,"reliability":0.9554946,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/h100price/static/exports/b300_rental_prices.xlsx
+++ b/h100price/static/exports/b300_rental_prices.xlsx
@@ -45306,6 +45306,1412 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G613">
+        <v>7.339259</v>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J613">
+        <v>1</v>
+      </c>
+      <c r="K613">
+        <v>7.339259</v>
+      </c>
+      <c r="L613">
+        <v>7.339259</v>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9657454,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G614">
+        <v>7.668148</v>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J614">
+        <v>1</v>
+      </c>
+      <c r="K614">
+        <v>7.668148</v>
+      </c>
+      <c r="L614">
+        <v>7.668148</v>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487077,"reliability":0.9192806,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G615">
+        <v>9.335556</v>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J615">
+        <v>1</v>
+      </c>
+      <c r="K615">
+        <v>9.335556</v>
+      </c>
+      <c r="L615">
+        <v>9.335556</v>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345028,"reliability":0.964355,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G616">
+        <v>14.668148</v>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J616">
+        <v>2</v>
+      </c>
+      <c r="K616">
+        <v>7.334074</v>
+      </c>
+      <c r="L616">
+        <v>7.334074</v>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9658661,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G617">
+        <v>15.334815</v>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J617">
+        <v>2</v>
+      </c>
+      <c r="K617">
+        <v>7.667407</v>
+      </c>
+      <c r="L617">
+        <v>7.667407</v>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487075,"reliability":0.9192806,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G618">
+        <v>17.877037</v>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J618">
+        <v>2</v>
+      </c>
+      <c r="K618">
+        <v>8.938519</v>
+      </c>
+      <c r="L618">
+        <v>8.938519</v>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456452,"reliability":0.9390298,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G619">
+        <v>18.668889</v>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J619">
+        <v>2</v>
+      </c>
+      <c r="K619">
+        <v>9.334444</v>
+      </c>
+      <c r="L619">
+        <v>9.334444</v>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345045,"reliability":0.9643525,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G620">
+        <v>18.668889</v>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J620">
+        <v>2</v>
+      </c>
+      <c r="K620">
+        <v>9.334444</v>
+      </c>
+      <c r="L620">
+        <v>9.334444</v>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345026,"reliability":0.964355,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G621">
+        <v>18.671111</v>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J621">
+        <v>2</v>
+      </c>
+      <c r="K621">
+        <v>9.335556</v>
+      </c>
+      <c r="L621">
+        <v>9.335556</v>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9850868,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G622">
+        <v>30.668148</v>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J622">
+        <v>4</v>
+      </c>
+      <c r="K622">
+        <v>7.667037</v>
+      </c>
+      <c r="L622">
+        <v>7.667037</v>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487081,"reliability":0.9192806,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G623">
+        <v>34.668148</v>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J623">
+        <v>4</v>
+      </c>
+      <c r="K623">
+        <v>8.667037</v>
+      </c>
+      <c r="L623">
+        <v>8.667037</v>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9184775,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G624">
+        <v>35.743704</v>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J624">
+        <v>4</v>
+      </c>
+      <c r="K624">
+        <v>8.935926</v>
+      </c>
+      <c r="L624">
+        <v>8.935926</v>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456453,"reliability":0.9390298,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G625">
+        <v>37.335556</v>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J625">
+        <v>4</v>
+      </c>
+      <c r="K625">
+        <v>9.333889</v>
+      </c>
+      <c r="L625">
+        <v>9.333889</v>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345042,"reliability":0.9643525,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G626">
+        <v>58.668148</v>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J626">
+        <v>8</v>
+      </c>
+      <c r="K626">
+        <v>7.333519</v>
+      </c>
+      <c r="L626">
+        <v>7.333519</v>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9650879,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G627">
+        <v>61.334815</v>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J627">
+        <v>8</v>
+      </c>
+      <c r="K627">
+        <v>7.666852</v>
+      </c>
+      <c r="L627">
+        <v>7.666852</v>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487082,"reliability":0.9192806,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G628">
+        <v>64.002222</v>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J628">
+        <v>8</v>
+      </c>
+      <c r="K628">
+        <v>8.000278</v>
+      </c>
+      <c r="L628">
+        <v>8.000278</v>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9608315,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G629">
+        <v>69.334815</v>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J629">
+        <v>8</v>
+      </c>
+      <c r="K629">
+        <v>8.666852</v>
+      </c>
+      <c r="L629">
+        <v>8.666852</v>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9184775,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G630">
+        <v>74.668889</v>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J630">
+        <v>8</v>
+      </c>
+      <c r="K630">
+        <v>9.333611</v>
+      </c>
+      <c r="L630">
+        <v>9.333611</v>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345052,"reliability":0.9643525,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G631">
+        <v>74.668889</v>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J631">
+        <v>8</v>
+      </c>
+      <c r="K631">
+        <v>9.333611</v>
+      </c>
+      <c r="L631">
+        <v>9.333611</v>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.964355,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/h100price/static/exports/b300_rental_prices.xlsx
+++ b/h100price/static/exports/b300_rental_prices.xlsx
@@ -67062,6 +67062,9774 @@
         </is>
       </c>
     </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G907">
+        <v>6.671111</v>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J907">
+        <v>1</v>
+      </c>
+      <c r="K907">
+        <v>6.671111</v>
+      </c>
+      <c r="L907">
+        <v>6.671111</v>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P907" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860217,"reliability":0.9817845,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G908">
+        <v>7.339259</v>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J908">
+        <v>1</v>
+      </c>
+      <c r="K908">
+        <v>7.339259</v>
+      </c>
+      <c r="L908">
+        <v>7.339259</v>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P908" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404969,"reliability":0.9699055,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G909">
+        <v>13.337778</v>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J909">
+        <v>2</v>
+      </c>
+      <c r="K909">
+        <v>6.668889</v>
+      </c>
+      <c r="L909">
+        <v>6.668889</v>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P909" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860225,"reliability":0.9817845,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G910">
+        <v>13.337778</v>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J910">
+        <v>2</v>
+      </c>
+      <c r="K910">
+        <v>6.668889</v>
+      </c>
+      <c r="L910">
+        <v>6.668889</v>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O910" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P910" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345049,"reliability":0.9651098,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G911">
+        <v>14.672593</v>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J911">
+        <v>2</v>
+      </c>
+      <c r="K911">
+        <v>7.336296</v>
+      </c>
+      <c r="L911">
+        <v>7.336296</v>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P911" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.9699055,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G912">
+        <v>18.671111</v>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J912">
+        <v>2</v>
+      </c>
+      <c r="K912">
+        <v>9.335556</v>
+      </c>
+      <c r="L912">
+        <v>9.335556</v>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P912" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430318,"reliability":0.9865491,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G913">
+        <v>26.668889</v>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J913">
+        <v>4</v>
+      </c>
+      <c r="K913">
+        <v>6.667222</v>
+      </c>
+      <c r="L913">
+        <v>6.667222</v>
+      </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O913" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P913" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9391394,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G914">
+        <v>26.671111</v>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J914">
+        <v>4</v>
+      </c>
+      <c r="K914">
+        <v>6.667778</v>
+      </c>
+      <c r="L914">
+        <v>6.667778</v>
+      </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O914" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P914" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345051,"reliability":0.9651098,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G915">
+        <v>37.337778</v>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J915">
+        <v>4</v>
+      </c>
+      <c r="K915">
+        <v>9.334444</v>
+      </c>
+      <c r="L915">
+        <v>9.334444</v>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O915" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P915" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9865491,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G916">
+        <v>53.335556</v>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J916">
+        <v>8</v>
+      </c>
+      <c r="K916">
+        <v>6.666944</v>
+      </c>
+      <c r="L916">
+        <v>6.666944</v>
+      </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O916" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P916" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9391394,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G917">
+        <v>53.337778</v>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J917">
+        <v>8</v>
+      </c>
+      <c r="K917">
+        <v>6.667222</v>
+      </c>
+      <c r="L917">
+        <v>6.667222</v>
+      </c>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O917" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P917" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860228,"reliability":0.9817845,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G918">
+        <v>53.337778</v>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J918">
+        <v>8</v>
+      </c>
+      <c r="K918">
+        <v>6.667222</v>
+      </c>
+      <c r="L918">
+        <v>6.667222</v>
+      </c>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O918" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P918" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9651083,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G919">
+        <v>56.005926</v>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J919">
+        <v>8</v>
+      </c>
+      <c r="K919">
+        <v>7.000741</v>
+      </c>
+      <c r="L919">
+        <v>7.000741</v>
+      </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O919" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P919" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.965718,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G920">
+        <v>58.672593</v>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J920">
+        <v>8</v>
+      </c>
+      <c r="K920">
+        <v>7.334074</v>
+      </c>
+      <c r="L920">
+        <v>7.334074</v>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O920" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P920" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9398383,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>20260531T155959Z</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>2026-05-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G921">
+        <v>64.002222</v>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J921">
+        <v>8</v>
+      </c>
+      <c r="K921">
+        <v>8.000278</v>
+      </c>
+      <c r="L921">
+        <v>8.000278</v>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O921" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P921" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9622842,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G922">
+        <v>6.671111</v>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J922">
+        <v>1</v>
+      </c>
+      <c r="K922">
+        <v>6.671111</v>
+      </c>
+      <c r="L922">
+        <v>6.671111</v>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O922" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P922" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860226,"reliability":0.9820619,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G923">
+        <v>7.339259</v>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J923">
+        <v>1</v>
+      </c>
+      <c r="K923">
+        <v>7.339259</v>
+      </c>
+      <c r="L923">
+        <v>7.339259</v>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P923" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9710691,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G924">
+        <v>13.337778</v>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J924">
+        <v>2</v>
+      </c>
+      <c r="K924">
+        <v>6.668889</v>
+      </c>
+      <c r="L924">
+        <v>6.668889</v>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O924" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P924" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860225,"reliability":0.9820619,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G925">
+        <v>13.337778</v>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J925">
+        <v>2</v>
+      </c>
+      <c r="K925">
+        <v>6.668889</v>
+      </c>
+      <c r="L925">
+        <v>6.668889</v>
+      </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O925" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P925" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345030,"reliability":0.9651783,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G926">
+        <v>14.672593</v>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J926">
+        <v>2</v>
+      </c>
+      <c r="K926">
+        <v>7.336296</v>
+      </c>
+      <c r="L926">
+        <v>7.336296</v>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O926" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P926" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9710691,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G927">
+        <v>18.671111</v>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J927">
+        <v>2</v>
+      </c>
+      <c r="K927">
+        <v>9.335556</v>
+      </c>
+      <c r="L927">
+        <v>9.335556</v>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O927" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P927" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9866986,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G928">
+        <v>26.668889</v>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J928">
+        <v>4</v>
+      </c>
+      <c r="K928">
+        <v>6.667222</v>
+      </c>
+      <c r="L928">
+        <v>6.667222</v>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O928" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9405275,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G929">
+        <v>26.671111</v>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J929">
+        <v>4</v>
+      </c>
+      <c r="K929">
+        <v>6.667778</v>
+      </c>
+      <c r="L929">
+        <v>6.667778</v>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O929" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P929" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9820619,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G930">
+        <v>37.337778</v>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J930">
+        <v>4</v>
+      </c>
+      <c r="K930">
+        <v>9.334444</v>
+      </c>
+      <c r="L930">
+        <v>9.334444</v>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O930" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P930" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9866986,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G931">
+        <v>53.335556</v>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J931">
+        <v>8</v>
+      </c>
+      <c r="K931">
+        <v>6.666944</v>
+      </c>
+      <c r="L931">
+        <v>6.666944</v>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O931" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P931" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9405275,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G932">
+        <v>53.337778</v>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J932">
+        <v>8</v>
+      </c>
+      <c r="K932">
+        <v>6.667222</v>
+      </c>
+      <c r="L932">
+        <v>6.667222</v>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O932" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P932" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9651783,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G933">
+        <v>56.005926</v>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J933">
+        <v>8</v>
+      </c>
+      <c r="K933">
+        <v>7.000741</v>
+      </c>
+      <c r="L933">
+        <v>7.000741</v>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O933" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P933" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9657828,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G934">
+        <v>58.672593</v>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J934">
+        <v>8</v>
+      </c>
+      <c r="K934">
+        <v>7.334074</v>
+      </c>
+      <c r="L934">
+        <v>7.334074</v>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O934" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P934" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9412195,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>20260531T183157Z</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>2026-05-31T18:31:59Z</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G935">
+        <v>64.002222</v>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J935">
+        <v>8</v>
+      </c>
+      <c r="K935">
+        <v>8.000278</v>
+      </c>
+      <c r="L935">
+        <v>8.000278</v>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O935" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P935" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9624275,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G936">
+        <v>6.671111</v>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J936">
+        <v>1</v>
+      </c>
+      <c r="K936">
+        <v>6.671111</v>
+      </c>
+      <c r="L936">
+        <v>6.671111</v>
+      </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O936" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P936" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860226,"reliability":0.9820619,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G937">
+        <v>7.339259</v>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J937">
+        <v>1</v>
+      </c>
+      <c r="K937">
+        <v>7.339259</v>
+      </c>
+      <c r="L937">
+        <v>7.339259</v>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O937" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P937" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404967,"reliability":0.9710691,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G938">
+        <v>13.337778</v>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J938">
+        <v>2</v>
+      </c>
+      <c r="K938">
+        <v>6.668889</v>
+      </c>
+      <c r="L938">
+        <v>6.668889</v>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O938" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P938" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860221,"reliability":0.9820619,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G939">
+        <v>13.337778</v>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J939">
+        <v>2</v>
+      </c>
+      <c r="K939">
+        <v>6.668889</v>
+      </c>
+      <c r="L939">
+        <v>6.668889</v>
+      </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O939" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P939" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345049,"reliability":0.9651802,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G940">
+        <v>14.672593</v>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J940">
+        <v>2</v>
+      </c>
+      <c r="K940">
+        <v>7.336296</v>
+      </c>
+      <c r="L940">
+        <v>7.336296</v>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O940" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P940" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9710691,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G941">
+        <v>18.671111</v>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J941">
+        <v>2</v>
+      </c>
+      <c r="K941">
+        <v>9.335556</v>
+      </c>
+      <c r="L941">
+        <v>9.335556</v>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O941" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P941" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9866986,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G942">
+        <v>26.668889</v>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J942">
+        <v>4</v>
+      </c>
+      <c r="K942">
+        <v>6.667222</v>
+      </c>
+      <c r="L942">
+        <v>6.667222</v>
+      </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O942" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P942" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.9405275,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G943">
+        <v>26.671111</v>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J943">
+        <v>4</v>
+      </c>
+      <c r="K943">
+        <v>6.667778</v>
+      </c>
+      <c r="L943">
+        <v>6.667778</v>
+      </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O943" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P943" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9820619,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G944">
+        <v>37.337778</v>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J944">
+        <v>4</v>
+      </c>
+      <c r="K944">
+        <v>9.334444</v>
+      </c>
+      <c r="L944">
+        <v>9.334444</v>
+      </c>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O944" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P944" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9866986,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G945">
+        <v>53.335556</v>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J945">
+        <v>8</v>
+      </c>
+      <c r="K945">
+        <v>6.666944</v>
+      </c>
+      <c r="L945">
+        <v>6.666944</v>
+      </c>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O945" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P945" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9405275,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G946">
+        <v>53.337778</v>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J946">
+        <v>8</v>
+      </c>
+      <c r="K946">
+        <v>6.667222</v>
+      </c>
+      <c r="L946">
+        <v>6.667222</v>
+      </c>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O946" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P946" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345052,"reliability":0.9651802,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G947">
+        <v>56.005926</v>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J947">
+        <v>8</v>
+      </c>
+      <c r="K947">
+        <v>7.000741</v>
+      </c>
+      <c r="L947">
+        <v>7.000741</v>
+      </c>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O947" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P947" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9657828,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G948">
+        <v>58.672593</v>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J948">
+        <v>8</v>
+      </c>
+      <c r="K948">
+        <v>7.334074</v>
+      </c>
+      <c r="L948">
+        <v>7.334074</v>
+      </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O948" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P948" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9412195,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>20260531T185959Z</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>2026-05-31T19:00:03Z</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G949">
+        <v>64.002222</v>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J949">
+        <v>8</v>
+      </c>
+      <c r="K949">
+        <v>8.000278</v>
+      </c>
+      <c r="L949">
+        <v>8.000278</v>
+      </c>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O949" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P949" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9624275,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G950">
+        <v>6.671111</v>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J950">
+        <v>1</v>
+      </c>
+      <c r="K950">
+        <v>6.671111</v>
+      </c>
+      <c r="L950">
+        <v>6.671111</v>
+      </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O950" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P950" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860223,"reliability":0.9821556,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G951">
+        <v>7.339259</v>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J951">
+        <v>1</v>
+      </c>
+      <c r="K951">
+        <v>7.339259</v>
+      </c>
+      <c r="L951">
+        <v>7.339259</v>
+      </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O951" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P951" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404967,"reliability":0.9714145,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G952">
+        <v>13.337778</v>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J952">
+        <v>2</v>
+      </c>
+      <c r="K952">
+        <v>6.668889</v>
+      </c>
+      <c r="L952">
+        <v>6.668889</v>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O952" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P952" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860225,"reliability":0.9821556,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G953">
+        <v>13.337778</v>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J953">
+        <v>2</v>
+      </c>
+      <c r="K953">
+        <v>6.668889</v>
+      </c>
+      <c r="L953">
+        <v>6.668889</v>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O953" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P953" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9652022,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G954">
+        <v>14.668148</v>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J954">
+        <v>2</v>
+      </c>
+      <c r="K954">
+        <v>7.334074</v>
+      </c>
+      <c r="L954">
+        <v>7.334074</v>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P954" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404986,"reliability":0.947972,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G955">
+        <v>14.672593</v>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J955">
+        <v>2</v>
+      </c>
+      <c r="K955">
+        <v>7.336296</v>
+      </c>
+      <c r="L955">
+        <v>7.336296</v>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O955" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P955" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9714145,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G956">
+        <v>18.671111</v>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J956">
+        <v>2</v>
+      </c>
+      <c r="K956">
+        <v>9.335556</v>
+      </c>
+      <c r="L956">
+        <v>9.335556</v>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P956" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430316,"reliability":0.9867449,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G957">
+        <v>26.668889</v>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J957">
+        <v>4</v>
+      </c>
+      <c r="K957">
+        <v>6.667222</v>
+      </c>
+      <c r="L957">
+        <v>6.667222</v>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O957" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P957" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.9409588,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G958">
+        <v>26.671111</v>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J958">
+        <v>4</v>
+      </c>
+      <c r="K958">
+        <v>6.667778</v>
+      </c>
+      <c r="L958">
+        <v>6.667778</v>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O958" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P958" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345023,"reliability":0.9652022,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G959">
+        <v>29.334815</v>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J959">
+        <v>4</v>
+      </c>
+      <c r="K959">
+        <v>7.333704</v>
+      </c>
+      <c r="L959">
+        <v>7.333704</v>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O959" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P959" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404987,"reliability":0.947972,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G960">
+        <v>37.337778</v>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J960">
+        <v>4</v>
+      </c>
+      <c r="K960">
+        <v>9.334444</v>
+      </c>
+      <c r="L960">
+        <v>9.334444</v>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O960" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P960" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9867449,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G961">
+        <v>53.335556</v>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J961">
+        <v>8</v>
+      </c>
+      <c r="K961">
+        <v>6.666944</v>
+      </c>
+      <c r="L961">
+        <v>6.666944</v>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P961" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9409588,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G962">
+        <v>53.337778</v>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J962">
+        <v>8</v>
+      </c>
+      <c r="K962">
+        <v>6.667222</v>
+      </c>
+      <c r="L962">
+        <v>6.667222</v>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P962" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9652022,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G963">
+        <v>58.668148</v>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J963">
+        <v>8</v>
+      </c>
+      <c r="K963">
+        <v>7.333519</v>
+      </c>
+      <c r="L963">
+        <v>7.333519</v>
+      </c>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P963" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404992,"reliability":0.947972,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G964">
+        <v>58.672593</v>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J964">
+        <v>8</v>
+      </c>
+      <c r="K964">
+        <v>7.334074</v>
+      </c>
+      <c r="L964">
+        <v>7.334074</v>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O964" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P964" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9416142,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>20260531T200357Z</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>2026-05-31T20:03:59Z</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G965">
+        <v>64.002222</v>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J965">
+        <v>8</v>
+      </c>
+      <c r="K965">
+        <v>8.000278</v>
+      </c>
+      <c r="L965">
+        <v>8.000278</v>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P965" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9624719,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G966">
+        <v>6.671111</v>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J966">
+        <v>1</v>
+      </c>
+      <c r="K966">
+        <v>6.671111</v>
+      </c>
+      <c r="L966">
+        <v>6.671111</v>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O966" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P966" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860224,"reliability":0.9824525,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G967">
+        <v>7.339259</v>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J967">
+        <v>1</v>
+      </c>
+      <c r="K967">
+        <v>7.339259</v>
+      </c>
+      <c r="L967">
+        <v>7.339259</v>
+      </c>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O967" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P967" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404972,"reliability":0.9724823,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G968">
+        <v>13.337778</v>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J968">
+        <v>2</v>
+      </c>
+      <c r="K968">
+        <v>6.668889</v>
+      </c>
+      <c r="L968">
+        <v>6.668889</v>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O968" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P968" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860225,"reliability":0.9824525,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G969">
+        <v>13.337778</v>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J969">
+        <v>2</v>
+      </c>
+      <c r="K969">
+        <v>6.668889</v>
+      </c>
+      <c r="L969">
+        <v>6.668889</v>
+      </c>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P969" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345040,"reliability":0.9652793,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G970">
+        <v>14.672593</v>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J970">
+        <v>2</v>
+      </c>
+      <c r="K970">
+        <v>7.336296</v>
+      </c>
+      <c r="L970">
+        <v>7.336296</v>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P970" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9724823,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G971">
+        <v>18.671111</v>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J971">
+        <v>2</v>
+      </c>
+      <c r="K971">
+        <v>9.335556</v>
+      </c>
+      <c r="L971">
+        <v>9.335556</v>
+      </c>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O971" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P971" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9868924,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G972">
+        <v>26.668889</v>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J972">
+        <v>4</v>
+      </c>
+      <c r="K972">
+        <v>6.667222</v>
+      </c>
+      <c r="L972">
+        <v>6.667222</v>
+      </c>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O972" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P972" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9422008,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G973">
+        <v>26.671111</v>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J973">
+        <v>4</v>
+      </c>
+      <c r="K973">
+        <v>6.667778</v>
+      </c>
+      <c r="L973">
+        <v>6.667778</v>
+      </c>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O973" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P973" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345042,"reliability":0.9652793,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G974">
+        <v>29.334815</v>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J974">
+        <v>4</v>
+      </c>
+      <c r="K974">
+        <v>7.333704</v>
+      </c>
+      <c r="L974">
+        <v>7.333704</v>
+      </c>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O974" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P974" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404991,"reliability":0.9487601,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G975">
+        <v>37.337778</v>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J975">
+        <v>4</v>
+      </c>
+      <c r="K975">
+        <v>9.334444</v>
+      </c>
+      <c r="L975">
+        <v>9.334444</v>
+      </c>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O975" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P975" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9868924,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G976">
+        <v>53.335556</v>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J976">
+        <v>8</v>
+      </c>
+      <c r="K976">
+        <v>6.666944</v>
+      </c>
+      <c r="L976">
+        <v>6.666944</v>
+      </c>
+      <c r="M976" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O976" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P976" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9422008,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G977">
+        <v>53.337778</v>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J977">
+        <v>8</v>
+      </c>
+      <c r="K977">
+        <v>6.667222</v>
+      </c>
+      <c r="L977">
+        <v>6.667222</v>
+      </c>
+      <c r="M977" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O977" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P977" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9652774,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G978">
+        <v>58.668148</v>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J978">
+        <v>8</v>
+      </c>
+      <c r="K978">
+        <v>7.333519</v>
+      </c>
+      <c r="L978">
+        <v>7.333519</v>
+      </c>
+      <c r="M978" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O978" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P978" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404992,"reliability":0.9487601,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G979">
+        <v>58.672593</v>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J979">
+        <v>8</v>
+      </c>
+      <c r="K979">
+        <v>7.334074</v>
+      </c>
+      <c r="L979">
+        <v>7.334074</v>
+      </c>
+      <c r="M979" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O979" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P979" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9428695,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>20260531T223115Z</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:31:17Z</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G980">
+        <v>64.002222</v>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J980">
+        <v>8</v>
+      </c>
+      <c r="K980">
+        <v>8.000278</v>
+      </c>
+      <c r="L980">
+        <v>8.000278</v>
+      </c>
+      <c r="M980" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O980" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P980" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9626102,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G981">
+        <v>6.671111</v>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J981">
+        <v>1</v>
+      </c>
+      <c r="K981">
+        <v>6.671111</v>
+      </c>
+      <c r="L981">
+        <v>6.671111</v>
+      </c>
+      <c r="M981" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O981" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P981" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345041,"reliability":0.9653059,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G982">
+        <v>7.339259</v>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J982">
+        <v>1</v>
+      </c>
+      <c r="K982">
+        <v>7.339259</v>
+      </c>
+      <c r="L982">
+        <v>7.339259</v>
+      </c>
+      <c r="M982" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O982" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P982" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404967,"reliability":0.9728134,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G983">
+        <v>13.337778</v>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J983">
+        <v>2</v>
+      </c>
+      <c r="K983">
+        <v>6.668889</v>
+      </c>
+      <c r="L983">
+        <v>6.668889</v>
+      </c>
+      <c r="M983" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O983" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P983" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860220,"reliability":0.9825502,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G984">
+        <v>13.337778</v>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J984">
+        <v>2</v>
+      </c>
+      <c r="K984">
+        <v>6.668889</v>
+      </c>
+      <c r="L984">
+        <v>6.668889</v>
+      </c>
+      <c r="M984" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O984" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P984" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345030,"reliability":0.9653041,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G985">
+        <v>14.668148</v>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J985">
+        <v>2</v>
+      </c>
+      <c r="K985">
+        <v>7.334074</v>
+      </c>
+      <c r="L985">
+        <v>7.334074</v>
+      </c>
+      <c r="M985" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O985" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P985" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404986,"reliability":0.9490379,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G986">
+        <v>18.671111</v>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J986">
+        <v>2</v>
+      </c>
+      <c r="K986">
+        <v>9.335556</v>
+      </c>
+      <c r="L986">
+        <v>9.335556</v>
+      </c>
+      <c r="M986" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N986" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O986" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P986" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430318,"reliability":0.9869422,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G987">
+        <v>26.668889</v>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J987">
+        <v>4</v>
+      </c>
+      <c r="K987">
+        <v>6.667222</v>
+      </c>
+      <c r="L987">
+        <v>6.667222</v>
+      </c>
+      <c r="M987" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N987" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O987" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P987" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.942619,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G988">
+        <v>26.671111</v>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J988">
+        <v>4</v>
+      </c>
+      <c r="K988">
+        <v>6.667778</v>
+      </c>
+      <c r="L988">
+        <v>6.667778</v>
+      </c>
+      <c r="M988" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N988" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O988" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P988" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345042,"reliability":0.9653059,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G989">
+        <v>29.334815</v>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J989">
+        <v>4</v>
+      </c>
+      <c r="K989">
+        <v>7.333704</v>
+      </c>
+      <c r="L989">
+        <v>7.333704</v>
+      </c>
+      <c r="M989" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N989" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O989" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P989" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404987,"reliability":0.9490379,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G990">
+        <v>37.337778</v>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J990">
+        <v>4</v>
+      </c>
+      <c r="K990">
+        <v>9.334444</v>
+      </c>
+      <c r="L990">
+        <v>9.334444</v>
+      </c>
+      <c r="M990" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N990" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O990" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P990" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9869422,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G991">
+        <v>53.335556</v>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J991">
+        <v>8</v>
+      </c>
+      <c r="K991">
+        <v>6.666944</v>
+      </c>
+      <c r="L991">
+        <v>6.666944</v>
+      </c>
+      <c r="M991" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N991" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O991" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P991" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.942619,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G992">
+        <v>53.337778</v>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J992">
+        <v>8</v>
+      </c>
+      <c r="K992">
+        <v>6.667222</v>
+      </c>
+      <c r="L992">
+        <v>6.667222</v>
+      </c>
+      <c r="M992" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N992" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O992" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P992" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9653041,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G993">
+        <v>58.668148</v>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J993">
+        <v>8</v>
+      </c>
+      <c r="K993">
+        <v>7.333519</v>
+      </c>
+      <c r="L993">
+        <v>7.333519</v>
+      </c>
+      <c r="M993" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N993" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O993" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P993" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404992,"reliability":0.9490379,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G994">
+        <v>58.672593</v>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J994">
+        <v>8</v>
+      </c>
+      <c r="K994">
+        <v>7.334074</v>
+      </c>
+      <c r="L994">
+        <v>7.334074</v>
+      </c>
+      <c r="M994" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N994" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O994" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P994" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9432942,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>20260531T234328Z</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>2026-05-31T23:43:29Z</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G995">
+        <v>64.002222</v>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J995">
+        <v>8</v>
+      </c>
+      <c r="K995">
+        <v>8.000278</v>
+      </c>
+      <c r="L995">
+        <v>8.000278</v>
+      </c>
+      <c r="M995" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N995" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O995" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P995" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9626604,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G996">
+        <v>6.671111</v>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J996">
+        <v>1</v>
+      </c>
+      <c r="K996">
+        <v>6.671111</v>
+      </c>
+      <c r="L996">
+        <v>6.671111</v>
+      </c>
+      <c r="M996" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N996" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O996" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P996" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860215,"reliability":0.9825502,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G997">
+        <v>7.339259</v>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J997">
+        <v>1</v>
+      </c>
+      <c r="K997">
+        <v>7.339259</v>
+      </c>
+      <c r="L997">
+        <v>7.339259</v>
+      </c>
+      <c r="M997" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N997" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O997" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P997" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404972,"reliability":0.9728134,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G998">
+        <v>13.337778</v>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J998">
+        <v>2</v>
+      </c>
+      <c r="K998">
+        <v>6.668889</v>
+      </c>
+      <c r="L998">
+        <v>6.668889</v>
+      </c>
+      <c r="M998" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N998" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O998" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P998" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860221,"reliability":0.9825502,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G999">
+        <v>13.337778</v>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J999">
+        <v>2</v>
+      </c>
+      <c r="K999">
+        <v>6.668889</v>
+      </c>
+      <c r="L999">
+        <v>6.668889</v>
+      </c>
+      <c r="M999" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N999" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O999" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P999" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9653041,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1000">
+        <v>14.668148</v>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1000">
+        <v>2</v>
+      </c>
+      <c r="K1000">
+        <v>7.334074</v>
+      </c>
+      <c r="L1000">
+        <v>7.334074</v>
+      </c>
+      <c r="M1000" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1000" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1000" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1000" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404990,"reliability":0.9490379,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1001">
+        <v>18.671111</v>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1001">
+        <v>2</v>
+      </c>
+      <c r="K1001">
+        <v>9.335556</v>
+      </c>
+      <c r="L1001">
+        <v>9.335556</v>
+      </c>
+      <c r="M1001" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1001" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1001" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1001" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9869422,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1002">
+        <v>26.668889</v>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1002">
+        <v>4</v>
+      </c>
+      <c r="K1002">
+        <v>6.667222</v>
+      </c>
+      <c r="L1002">
+        <v>6.667222</v>
+      </c>
+      <c r="M1002" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1002" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1002" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1002" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.942619,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1003">
+        <v>26.671111</v>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1003">
+        <v>4</v>
+      </c>
+      <c r="K1003">
+        <v>6.667778</v>
+      </c>
+      <c r="L1003">
+        <v>6.667778</v>
+      </c>
+      <c r="M1003" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1003" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1003" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1003" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9825502,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1004">
+        <v>29.334815</v>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1004">
+        <v>4</v>
+      </c>
+      <c r="K1004">
+        <v>7.333704</v>
+      </c>
+      <c r="L1004">
+        <v>7.333704</v>
+      </c>
+      <c r="M1004" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1004" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1004" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1004" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404987,"reliability":0.9490379,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1005">
+        <v>37.337778</v>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1005">
+        <v>4</v>
+      </c>
+      <c r="K1005">
+        <v>9.334444</v>
+      </c>
+      <c r="L1005">
+        <v>9.334444</v>
+      </c>
+      <c r="M1005" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1005" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1005" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1005" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9869422,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1006">
+        <v>53.335556</v>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1006">
+        <v>8</v>
+      </c>
+      <c r="K1006">
+        <v>6.666944</v>
+      </c>
+      <c r="L1006">
+        <v>6.666944</v>
+      </c>
+      <c r="M1006" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1006" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1006" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1006" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.942619,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1007">
+        <v>53.337778</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1007">
+        <v>8</v>
+      </c>
+      <c r="K1007">
+        <v>6.667222</v>
+      </c>
+      <c r="L1007">
+        <v>6.667222</v>
+      </c>
+      <c r="M1007" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1007" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1007" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1007" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9653041,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1008">
+        <v>58.668148</v>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1008">
+        <v>8</v>
+      </c>
+      <c r="K1008">
+        <v>7.333519</v>
+      </c>
+      <c r="L1008">
+        <v>7.333519</v>
+      </c>
+      <c r="M1008" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1008" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1008" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1008" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404992,"reliability":0.9490379,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1009">
+        <v>58.672593</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1009">
+        <v>8</v>
+      </c>
+      <c r="K1009">
+        <v>7.334074</v>
+      </c>
+      <c r="L1009">
+        <v>7.334074</v>
+      </c>
+      <c r="M1009" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1009" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1009" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1009" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9432942,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>20260531T235959Z</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>2026-06-01T00:00:03Z</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1010">
+        <v>64.002222</v>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1010">
+        <v>8</v>
+      </c>
+      <c r="K1010">
+        <v>8.000278</v>
+      </c>
+      <c r="L1010">
+        <v>8.000278</v>
+      </c>
+      <c r="M1010" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1010" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1010" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1010" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9626604,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1011">
+        <v>6.671111</v>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1011">
+        <v>1</v>
+      </c>
+      <c r="K1011">
+        <v>6.671111</v>
+      </c>
+      <c r="L1011">
+        <v>6.671111</v>
+      </c>
+      <c r="M1011" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1011" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1011" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1011" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860215,"reliability":0.9827373,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1012">
+        <v>7.339259</v>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1012">
+        <v>1</v>
+      </c>
+      <c r="K1012">
+        <v>7.339259</v>
+      </c>
+      <c r="L1012">
+        <v>7.339259</v>
+      </c>
+      <c r="M1012" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1012" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1012" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1012" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9734394,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1013">
+        <v>13.337778</v>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1013">
+        <v>2</v>
+      </c>
+      <c r="K1013">
+        <v>6.668889</v>
+      </c>
+      <c r="L1013">
+        <v>6.668889</v>
+      </c>
+      <c r="M1013" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1013" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1013" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1013" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860225,"reliability":0.9827373,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1014">
+        <v>13.337778</v>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1014">
+        <v>2</v>
+      </c>
+      <c r="K1014">
+        <v>6.668889</v>
+      </c>
+      <c r="L1014">
+        <v>6.668889</v>
+      </c>
+      <c r="M1014" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1014" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1014" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1014" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345045,"reliability":0.9653554,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1015">
+        <v>14.672593</v>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1015">
+        <v>2</v>
+      </c>
+      <c r="K1015">
+        <v>7.336296</v>
+      </c>
+      <c r="L1015">
+        <v>7.336296</v>
+      </c>
+      <c r="M1015" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1015" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1015" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1015" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9734394,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1016">
+        <v>18.671111</v>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1016">
+        <v>2</v>
+      </c>
+      <c r="K1016">
+        <v>9.335556</v>
+      </c>
+      <c r="L1016">
+        <v>9.335556</v>
+      </c>
+      <c r="M1016" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1016" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1016" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1016" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9870374,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1017">
+        <v>26.668889</v>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1017">
+        <v>4</v>
+      </c>
+      <c r="K1017">
+        <v>6.667222</v>
+      </c>
+      <c r="L1017">
+        <v>6.667222</v>
+      </c>
+      <c r="M1017" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1017" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1017" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1017" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9433696,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1018">
+        <v>26.671111</v>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1018">
+        <v>4</v>
+      </c>
+      <c r="K1018">
+        <v>6.667778</v>
+      </c>
+      <c r="L1018">
+        <v>6.667778</v>
+      </c>
+      <c r="M1018" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1018" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1018" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1018" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9827373,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1019">
+        <v>37.337778</v>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1019">
+        <v>4</v>
+      </c>
+      <c r="K1019">
+        <v>9.334444</v>
+      </c>
+      <c r="L1019">
+        <v>9.334444</v>
+      </c>
+      <c r="M1019" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1019" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1019" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1019" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9870374,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1020">
+        <v>53.335556</v>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1020">
+        <v>8</v>
+      </c>
+      <c r="K1020">
+        <v>6.666944</v>
+      </c>
+      <c r="L1020">
+        <v>6.666944</v>
+      </c>
+      <c r="M1020" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1020" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1020" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1020" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9433696,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1021">
+        <v>53.337778</v>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1021">
+        <v>8</v>
+      </c>
+      <c r="K1021">
+        <v>6.667222</v>
+      </c>
+      <c r="L1021">
+        <v>6.667222</v>
+      </c>
+      <c r="M1021" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1021" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1021" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1021" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345052,"reliability":0.9653554,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1022">
+        <v>56.005926</v>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1022">
+        <v>8</v>
+      </c>
+      <c r="K1022">
+        <v>7.000741</v>
+      </c>
+      <c r="L1022">
+        <v>7.000741</v>
+      </c>
+      <c r="M1022" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1022" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1022" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1022" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9659318,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1023">
+        <v>58.672593</v>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1023">
+        <v>8</v>
+      </c>
+      <c r="K1023">
+        <v>7.334074</v>
+      </c>
+      <c r="L1023">
+        <v>7.334074</v>
+      </c>
+      <c r="M1023" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1023" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1023" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1023" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9440642,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>20260601T013451Z</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>2026-06-01T01:34:53Z</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1024">
+        <v>64.002222</v>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1024">
+        <v>8</v>
+      </c>
+      <c r="K1024">
+        <v>8.000278</v>
+      </c>
+      <c r="L1024">
+        <v>8.000278</v>
+      </c>
+      <c r="M1024" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1024" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1024" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1024" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.962752,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1025">
+        <v>6.671111</v>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1025">
+        <v>1</v>
+      </c>
+      <c r="K1025">
+        <v>6.671111</v>
+      </c>
+      <c r="L1025">
+        <v>6.671111</v>
+      </c>
+      <c r="M1025" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1025" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1025" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1025" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860217,"reliability":0.9827373,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1026">
+        <v>7.339259</v>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1026">
+        <v>1</v>
+      </c>
+      <c r="K1026">
+        <v>7.339259</v>
+      </c>
+      <c r="L1026">
+        <v>7.339259</v>
+      </c>
+      <c r="M1026" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1026" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1026" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1026" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404967,"reliability":0.9734394,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1027">
+        <v>13.337778</v>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1027">
+        <v>2</v>
+      </c>
+      <c r="K1027">
+        <v>6.668889</v>
+      </c>
+      <c r="L1027">
+        <v>6.668889</v>
+      </c>
+      <c r="M1027" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1027" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1027" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1027" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860225,"reliability":0.9827373,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1028">
+        <v>13.337778</v>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1028">
+        <v>2</v>
+      </c>
+      <c r="K1028">
+        <v>6.668889</v>
+      </c>
+      <c r="L1028">
+        <v>6.668889</v>
+      </c>
+      <c r="M1028" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1028" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1028" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1028" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345049,"reliability":0.9653554,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1029">
+        <v>14.672593</v>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1029">
+        <v>2</v>
+      </c>
+      <c r="K1029">
+        <v>7.336296</v>
+      </c>
+      <c r="L1029">
+        <v>7.336296</v>
+      </c>
+      <c r="M1029" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1029" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1029" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1029" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9734394,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1030">
+        <v>18.671111</v>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1030">
+        <v>2</v>
+      </c>
+      <c r="K1030">
+        <v>9.335556</v>
+      </c>
+      <c r="L1030">
+        <v>9.335556</v>
+      </c>
+      <c r="M1030" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1030" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1030" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1030" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9870374,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1031">
+        <v>26.668889</v>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1031">
+        <v>4</v>
+      </c>
+      <c r="K1031">
+        <v>6.667222</v>
+      </c>
+      <c r="L1031">
+        <v>6.667222</v>
+      </c>
+      <c r="M1031" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1031" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1031" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1031" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9433696,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1032">
+        <v>26.671111</v>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1032">
+        <v>4</v>
+      </c>
+      <c r="K1032">
+        <v>6.667778</v>
+      </c>
+      <c r="L1032">
+        <v>6.667778</v>
+      </c>
+      <c r="M1032" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1032" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1032" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1032" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9827373,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1033">
+        <v>37.337778</v>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1033">
+        <v>4</v>
+      </c>
+      <c r="K1033">
+        <v>9.334444</v>
+      </c>
+      <c r="L1033">
+        <v>9.334444</v>
+      </c>
+      <c r="M1033" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1033" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1033" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1033" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9870374,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1034">
+        <v>53.335556</v>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1034">
+        <v>8</v>
+      </c>
+      <c r="K1034">
+        <v>6.666944</v>
+      </c>
+      <c r="L1034">
+        <v>6.666944</v>
+      </c>
+      <c r="M1034" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1034" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1034" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1034" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9433696,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1035">
+        <v>53.337778</v>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1035">
+        <v>8</v>
+      </c>
+      <c r="K1035">
+        <v>6.667222</v>
+      </c>
+      <c r="L1035">
+        <v>6.667222</v>
+      </c>
+      <c r="M1035" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1035" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1035" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1035" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345052,"reliability":0.9653554,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1036">
+        <v>56.005926</v>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1036">
+        <v>8</v>
+      </c>
+      <c r="K1036">
+        <v>7.000741</v>
+      </c>
+      <c r="L1036">
+        <v>7.000741</v>
+      </c>
+      <c r="M1036" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1036" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1036" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1036" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9659318,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1037">
+        <v>58.672593</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1037">
+        <v>8</v>
+      </c>
+      <c r="K1037">
+        <v>7.334074</v>
+      </c>
+      <c r="L1037">
+        <v>7.334074</v>
+      </c>
+      <c r="M1037" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1037" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1037" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1037" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9440642,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>20260601T015959Z</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:00:01Z</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1038">
+        <v>64.002222</v>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1038">
+        <v>8</v>
+      </c>
+      <c r="K1038">
+        <v>8.000278</v>
+      </c>
+      <c r="L1038">
+        <v>8.000278</v>
+      </c>
+      <c r="M1038" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1038" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1038" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1038" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.962752,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/h100price/static/exports/b300_rental_prices.xlsx
+++ b/h100price/static/exports/b300_rental_prices.xlsx
@@ -76830,6 +76830,7258 @@
         </is>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1039">
+        <v>6.671111</v>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1039">
+        <v>1</v>
+      </c>
+      <c r="K1039">
+        <v>6.671111</v>
+      </c>
+      <c r="L1039">
+        <v>6.671111</v>
+      </c>
+      <c r="M1039" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1039" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1039" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1039" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860223,"reliability":0.9828255,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1040">
+        <v>7.339259</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1040">
+        <v>1</v>
+      </c>
+      <c r="K1040">
+        <v>7.339259</v>
+      </c>
+      <c r="L1040">
+        <v>7.339259</v>
+      </c>
+      <c r="M1040" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1040" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1040" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1040" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9737301,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1041">
+        <v>13.337778</v>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1041">
+        <v>2</v>
+      </c>
+      <c r="K1041">
+        <v>6.668889</v>
+      </c>
+      <c r="L1041">
+        <v>6.668889</v>
+      </c>
+      <c r="M1041" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1041" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1041" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1041" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860225,"reliability":0.9828255,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1042">
+        <v>13.337778</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1042">
+        <v>2</v>
+      </c>
+      <c r="K1042">
+        <v>6.668889</v>
+      </c>
+      <c r="L1042">
+        <v>6.668889</v>
+      </c>
+      <c r="M1042" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1042" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1042" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1042" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345044,"reliability":0.9653791,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1043">
+        <v>14.672593</v>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1043">
+        <v>2</v>
+      </c>
+      <c r="K1043">
+        <v>7.336296</v>
+      </c>
+      <c r="L1043">
+        <v>7.336296</v>
+      </c>
+      <c r="M1043" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1043" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1043" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1043" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9737301,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1044">
+        <v>18.671111</v>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1044">
+        <v>2</v>
+      </c>
+      <c r="K1044">
+        <v>9.335556</v>
+      </c>
+      <c r="L1044">
+        <v>9.335556</v>
+      </c>
+      <c r="M1044" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1044" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1044" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1044" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430316,"reliability":0.9870828,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1045">
+        <v>26.668889</v>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1045">
+        <v>4</v>
+      </c>
+      <c r="K1045">
+        <v>6.667222</v>
+      </c>
+      <c r="L1045">
+        <v>6.667222</v>
+      </c>
+      <c r="M1045" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1045" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1045" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1045" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9437488,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1046">
+        <v>26.671111</v>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1046">
+        <v>4</v>
+      </c>
+      <c r="K1046">
+        <v>6.667778</v>
+      </c>
+      <c r="L1046">
+        <v>6.667778</v>
+      </c>
+      <c r="M1046" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1046" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1046" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1046" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345042,"reliability":0.9653791,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1047">
+        <v>37.337778</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1047">
+        <v>4</v>
+      </c>
+      <c r="K1047">
+        <v>9.334444</v>
+      </c>
+      <c r="L1047">
+        <v>9.334444</v>
+      </c>
+      <c r="M1047" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1047" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1047" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1047" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9870828,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1048">
+        <v>53.335556</v>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1048">
+        <v>8</v>
+      </c>
+      <c r="K1048">
+        <v>6.666944</v>
+      </c>
+      <c r="L1048">
+        <v>6.666944</v>
+      </c>
+      <c r="M1048" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1048" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1048" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1048" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9437488,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1049">
+        <v>56.005926</v>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1049">
+        <v>8</v>
+      </c>
+      <c r="K1049">
+        <v>7.000741</v>
+      </c>
+      <c r="L1049">
+        <v>7.000741</v>
+      </c>
+      <c r="M1049" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1049" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1049" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1049" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.965952,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1050">
+        <v>58.672593</v>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1050">
+        <v>8</v>
+      </c>
+      <c r="K1050">
+        <v>7.334074</v>
+      </c>
+      <c r="L1050">
+        <v>7.334074</v>
+      </c>
+      <c r="M1050" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1050" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1050" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1050" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9444198,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>20260601T025959Z</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>2026-06-01T03:00:06Z</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1051">
+        <v>64.002222</v>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1051">
+        <v>8</v>
+      </c>
+      <c r="K1051">
+        <v>8.000278</v>
+      </c>
+      <c r="L1051">
+        <v>8.000278</v>
+      </c>
+      <c r="M1051" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1051" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1051" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1051" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9627945,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1052">
+        <v>6.671111</v>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1052">
+        <v>1</v>
+      </c>
+      <c r="K1052">
+        <v>6.671111</v>
+      </c>
+      <c r="L1052">
+        <v>6.671111</v>
+      </c>
+      <c r="M1052" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1052" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1052" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1052" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345029,"reliability":0.9682019,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1053">
+        <v>6.671111</v>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1053">
+        <v>1</v>
+      </c>
+      <c r="K1053">
+        <v>6.671111</v>
+      </c>
+      <c r="L1053">
+        <v>6.671111</v>
+      </c>
+      <c r="M1053" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1053" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1053" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1053" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345039,"reliability":0.9654513,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1054">
+        <v>7.339259</v>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1054">
+        <v>1</v>
+      </c>
+      <c r="K1054">
+        <v>7.339259</v>
+      </c>
+      <c r="L1054">
+        <v>7.339259</v>
+      </c>
+      <c r="M1054" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1054" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1054" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1054" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.974591,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1055">
+        <v>13.337778</v>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1055">
+        <v>2</v>
+      </c>
+      <c r="K1055">
+        <v>6.668889</v>
+      </c>
+      <c r="L1055">
+        <v>6.668889</v>
+      </c>
+      <c r="M1055" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1055" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1055" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1055" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345026,"reliability":0.9682019,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1056">
+        <v>13.337778</v>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1056">
+        <v>2</v>
+      </c>
+      <c r="K1056">
+        <v>6.668889</v>
+      </c>
+      <c r="L1056">
+        <v>6.668889</v>
+      </c>
+      <c r="M1056" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1056" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1056" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1056" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860220,"reliability":0.9830954,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1057">
+        <v>13.337778</v>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1057">
+        <v>2</v>
+      </c>
+      <c r="K1057">
+        <v>6.668889</v>
+      </c>
+      <c r="L1057">
+        <v>6.668889</v>
+      </c>
+      <c r="M1057" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1057" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1057" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1057" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345049,"reliability":0.9654513,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1058">
+        <v>14.672593</v>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1058">
+        <v>2</v>
+      </c>
+      <c r="K1058">
+        <v>7.336296</v>
+      </c>
+      <c r="L1058">
+        <v>7.336296</v>
+      </c>
+      <c r="M1058" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1058" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1058" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1058" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.974591,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1059">
+        <v>26.668889</v>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1059">
+        <v>4</v>
+      </c>
+      <c r="K1059">
+        <v>6.667222</v>
+      </c>
+      <c r="L1059">
+        <v>6.667222</v>
+      </c>
+      <c r="M1059" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1059" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1059" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1059" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.944836,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1060">
+        <v>26.671111</v>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1060">
+        <v>4</v>
+      </c>
+      <c r="K1060">
+        <v>6.667778</v>
+      </c>
+      <c r="L1060">
+        <v>6.667778</v>
+      </c>
+      <c r="M1060" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1060" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1060" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1060" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345051,"reliability":0.9654513,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1061">
+        <v>37.337778</v>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1061">
+        <v>4</v>
+      </c>
+      <c r="K1061">
+        <v>9.334444</v>
+      </c>
+      <c r="L1061">
+        <v>9.334444</v>
+      </c>
+      <c r="M1061" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1061" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1061" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1061" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9872212,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1062">
+        <v>53.335556</v>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1062">
+        <v>8</v>
+      </c>
+      <c r="K1062">
+        <v>6.666944</v>
+      </c>
+      <c r="L1062">
+        <v>6.666944</v>
+      </c>
+      <c r="M1062" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1062" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1062" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1062" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.944836,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1063">
+        <v>56.005926</v>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1063">
+        <v>8</v>
+      </c>
+      <c r="K1063">
+        <v>7.000741</v>
+      </c>
+      <c r="L1063">
+        <v>7.000741</v>
+      </c>
+      <c r="M1063" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1063" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1063" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1063" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.966013,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1064">
+        <v>58.672593</v>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1064">
+        <v>8</v>
+      </c>
+      <c r="K1064">
+        <v>7.334074</v>
+      </c>
+      <c r="L1064">
+        <v>7.334074</v>
+      </c>
+      <c r="M1064" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1064" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1064" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1064" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9454623,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>20260601T054057Z</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:40:59Z</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1065">
+        <v>64.002222</v>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1065">
+        <v>8</v>
+      </c>
+      <c r="K1065">
+        <v>8.000278</v>
+      </c>
+      <c r="L1065">
+        <v>8.000278</v>
+      </c>
+      <c r="M1065" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1065" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1065" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1065" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.962926,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1066">
+        <v>6.671111</v>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1066">
+        <v>1</v>
+      </c>
+      <c r="K1066">
+        <v>6.671111</v>
+      </c>
+      <c r="L1066">
+        <v>6.671111</v>
+      </c>
+      <c r="M1066" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1066" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1066" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1066" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860229,"reliability":0.9831819,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1067">
+        <v>6.868889</v>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1067">
+        <v>1</v>
+      </c>
+      <c r="K1067">
+        <v>6.868889</v>
+      </c>
+      <c r="L1067">
+        <v>6.868889</v>
+      </c>
+      <c r="M1067" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1067" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1067" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1067" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345031,"reliability":0.9689492,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1068">
+        <v>7.339259</v>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1068">
+        <v>1</v>
+      </c>
+      <c r="K1068">
+        <v>7.339259</v>
+      </c>
+      <c r="L1068">
+        <v>7.339259</v>
+      </c>
+      <c r="M1068" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1068" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1068" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1068" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9748587,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1069">
+        <v>13.337778</v>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1069">
+        <v>2</v>
+      </c>
+      <c r="K1069">
+        <v>6.668889</v>
+      </c>
+      <c r="L1069">
+        <v>6.668889</v>
+      </c>
+      <c r="M1069" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1069" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1069" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1069" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860220,"reliability":0.9831819,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1070">
+        <v>13.337778</v>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1070">
+        <v>2</v>
+      </c>
+      <c r="K1070">
+        <v>6.668889</v>
+      </c>
+      <c r="L1070">
+        <v>6.668889</v>
+      </c>
+      <c r="M1070" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1070" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1070" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1070" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345045,"reliability":0.9654749,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1071">
+        <v>13.735556</v>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1071">
+        <v>2</v>
+      </c>
+      <c r="K1071">
+        <v>6.867778</v>
+      </c>
+      <c r="L1071">
+        <v>6.867778</v>
+      </c>
+      <c r="M1071" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1071" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1071" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1071" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9689492,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1072">
+        <v>14.672593</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1072">
+        <v>2</v>
+      </c>
+      <c r="K1072">
+        <v>7.336296</v>
+      </c>
+      <c r="L1072">
+        <v>7.336296</v>
+      </c>
+      <c r="M1072" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1072" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1072" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1072" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9748587,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1073">
+        <v>26.668889</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1073">
+        <v>4</v>
+      </c>
+      <c r="K1073">
+        <v>6.667222</v>
+      </c>
+      <c r="L1073">
+        <v>6.667222</v>
+      </c>
+      <c r="M1073" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1073" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1073" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1073" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9451725,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1074">
+        <v>26.671111</v>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1074">
+        <v>4</v>
+      </c>
+      <c r="K1074">
+        <v>6.667778</v>
+      </c>
+      <c r="L1074">
+        <v>6.667778</v>
+      </c>
+      <c r="M1074" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1074" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1074" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1074" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9831819,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1075">
+        <v>37.337778</v>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1075">
+        <v>4</v>
+      </c>
+      <c r="K1075">
+        <v>9.334444</v>
+      </c>
+      <c r="L1075">
+        <v>9.334444</v>
+      </c>
+      <c r="M1075" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1075" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1075" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1075" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9872666,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1076">
+        <v>53.335556</v>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1076">
+        <v>8</v>
+      </c>
+      <c r="K1076">
+        <v>6.666944</v>
+      </c>
+      <c r="L1076">
+        <v>6.666944</v>
+      </c>
+      <c r="M1076" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1076" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1076" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1076" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9451725,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1077">
+        <v>56.005926</v>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1077">
+        <v>8</v>
+      </c>
+      <c r="K1077">
+        <v>7.000741</v>
+      </c>
+      <c r="L1077">
+        <v>7.000741</v>
+      </c>
+      <c r="M1077" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1077" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1077" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1077" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9660331,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1078">
+        <v>58.672593</v>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1078">
+        <v>8</v>
+      </c>
+      <c r="K1078">
+        <v>7.334074</v>
+      </c>
+      <c r="L1078">
+        <v>7.334074</v>
+      </c>
+      <c r="M1078" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1078" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1078" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1078" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9457909,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>20260601T065959Z</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1079">
+        <v>64.002222</v>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1079">
+        <v>8</v>
+      </c>
+      <c r="K1079">
+        <v>8.000278</v>
+      </c>
+      <c r="L1079">
+        <v>8.000278</v>
+      </c>
+      <c r="M1079" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1079" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1079" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1079" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9629688,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1080">
+        <v>6.671111</v>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1080">
+        <v>1</v>
+      </c>
+      <c r="K1080">
+        <v>6.671111</v>
+      </c>
+      <c r="L1080">
+        <v>6.671111</v>
+      </c>
+      <c r="M1080" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1080" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1080" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1080" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860223,"reliability":0.9834065,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1081">
+        <v>7.055556</v>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1081">
+        <v>1</v>
+      </c>
+      <c r="K1081">
+        <v>7.055556</v>
+      </c>
+      <c r="L1081">
+        <v>7.055556</v>
+      </c>
+      <c r="M1081" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1081" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1081" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1081" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345029,"reliability":0.9698361,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1082">
+        <v>7.339259</v>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1082">
+        <v>1</v>
+      </c>
+      <c r="K1082">
+        <v>7.339259</v>
+      </c>
+      <c r="L1082">
+        <v>7.339259</v>
+      </c>
+      <c r="M1082" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1082" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1082" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1082" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9756727,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1083">
+        <v>13.337778</v>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1083">
+        <v>2</v>
+      </c>
+      <c r="K1083">
+        <v>6.668889</v>
+      </c>
+      <c r="L1083">
+        <v>6.668889</v>
+      </c>
+      <c r="M1083" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1083" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1083" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1083" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860220,"reliability":0.9834065,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1084">
+        <v>13.337778</v>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1084">
+        <v>2</v>
+      </c>
+      <c r="K1084">
+        <v>6.668889</v>
+      </c>
+      <c r="L1084">
+        <v>6.668889</v>
+      </c>
+      <c r="M1084" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1084" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1084" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1084" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345044,"reliability":0.9651081,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1085">
+        <v>14.672593</v>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1085">
+        <v>2</v>
+      </c>
+      <c r="K1085">
+        <v>7.336296</v>
+      </c>
+      <c r="L1085">
+        <v>7.336296</v>
+      </c>
+      <c r="M1085" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1085" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1085" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1085" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9756727,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1086">
+        <v>18.671111</v>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1086">
+        <v>2</v>
+      </c>
+      <c r="K1086">
+        <v>9.335556</v>
+      </c>
+      <c r="L1086">
+        <v>9.335556</v>
+      </c>
+      <c r="M1086" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1086" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1086" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1086" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430316,"reliability":0.9871163,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1087">
+        <v>26.668889</v>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1087">
+        <v>4</v>
+      </c>
+      <c r="K1087">
+        <v>6.667222</v>
+      </c>
+      <c r="L1087">
+        <v>6.667222</v>
+      </c>
+      <c r="M1087" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1087" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1087" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1087" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9461276,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1088">
+        <v>26.671111</v>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1088">
+        <v>4</v>
+      </c>
+      <c r="K1088">
+        <v>6.667778</v>
+      </c>
+      <c r="L1088">
+        <v>6.667778</v>
+      </c>
+      <c r="M1088" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1088" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1088" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1088" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9834065,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1089">
+        <v>28.215556</v>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1089">
+        <v>4</v>
+      </c>
+      <c r="K1089">
+        <v>7.053889</v>
+      </c>
+      <c r="L1089">
+        <v>7.053889</v>
+      </c>
+      <c r="M1089" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1089" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1089" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1089" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345032,"reliability":0.9698361,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1090">
+        <v>29.339259</v>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1090">
+        <v>4</v>
+      </c>
+      <c r="K1090">
+        <v>7.334815</v>
+      </c>
+      <c r="L1090">
+        <v>7.334815</v>
+      </c>
+      <c r="M1090" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1090" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1090" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1090" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9756727,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1091">
+        <v>53.335556</v>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1091">
+        <v>8</v>
+      </c>
+      <c r="K1091">
+        <v>6.666944</v>
+      </c>
+      <c r="L1091">
+        <v>6.666944</v>
+      </c>
+      <c r="M1091" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1091" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1091" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1091" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9461276,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1092">
+        <v>56.005926</v>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1092">
+        <v>8</v>
+      </c>
+      <c r="K1092">
+        <v>7.000741</v>
+      </c>
+      <c r="L1092">
+        <v>7.000741</v>
+      </c>
+      <c r="M1092" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1092" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1092" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1092" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9660938,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1093">
+        <v>58.672593</v>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1093">
+        <v>8</v>
+      </c>
+      <c r="K1093">
+        <v>7.334074</v>
+      </c>
+      <c r="L1093">
+        <v>7.334074</v>
+      </c>
+      <c r="M1093" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1093" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1093" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1093" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9467472,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>20260601T095715Z</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:57:17Z</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1094">
+        <v>64.002222</v>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1094">
+        <v>8</v>
+      </c>
+      <c r="K1094">
+        <v>8.000278</v>
+      </c>
+      <c r="L1094">
+        <v>8.000278</v>
+      </c>
+      <c r="M1094" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1094" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1094" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1094" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9630974,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1095">
+        <v>6.671111</v>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1095">
+        <v>1</v>
+      </c>
+      <c r="K1095">
+        <v>6.671111</v>
+      </c>
+      <c r="L1095">
+        <v>6.671111</v>
+      </c>
+      <c r="M1095" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1095" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1095" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1095" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860217,"reliability":0.9834065,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1096">
+        <v>7.055556</v>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1096">
+        <v>1</v>
+      </c>
+      <c r="K1096">
+        <v>7.055556</v>
+      </c>
+      <c r="L1096">
+        <v>7.055556</v>
+      </c>
+      <c r="M1096" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1096" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1096" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1096" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345028,"reliability":0.9698361,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1097">
+        <v>7.339259</v>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1097">
+        <v>1</v>
+      </c>
+      <c r="K1097">
+        <v>7.339259</v>
+      </c>
+      <c r="L1097">
+        <v>7.339259</v>
+      </c>
+      <c r="M1097" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1097" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1097" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1097" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404969,"reliability":0.9756727,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1098">
+        <v>13.337778</v>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1098">
+        <v>2</v>
+      </c>
+      <c r="K1098">
+        <v>6.668889</v>
+      </c>
+      <c r="L1098">
+        <v>6.668889</v>
+      </c>
+      <c r="M1098" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1098" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1098" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1098" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860221,"reliability":0.9834065,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1099">
+        <v>13.337778</v>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1099">
+        <v>2</v>
+      </c>
+      <c r="K1099">
+        <v>6.668889</v>
+      </c>
+      <c r="L1099">
+        <v>6.668889</v>
+      </c>
+      <c r="M1099" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1099" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1099" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1099" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345045,"reliability":0.9651081,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1100">
+        <v>14.672593</v>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1100">
+        <v>2</v>
+      </c>
+      <c r="K1100">
+        <v>7.336296</v>
+      </c>
+      <c r="L1100">
+        <v>7.336296</v>
+      </c>
+      <c r="M1100" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1100" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1100" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1100" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.9756727,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1101">
+        <v>18.671111</v>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1101">
+        <v>2</v>
+      </c>
+      <c r="K1101">
+        <v>9.335556</v>
+      </c>
+      <c r="L1101">
+        <v>9.335556</v>
+      </c>
+      <c r="M1101" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1101" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1101" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1101" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9871163,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1102">
+        <v>26.668889</v>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1102">
+        <v>4</v>
+      </c>
+      <c r="K1102">
+        <v>6.667222</v>
+      </c>
+      <c r="L1102">
+        <v>6.667222</v>
+      </c>
+      <c r="M1102" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1102" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1102" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1102" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.9461276,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1103">
+        <v>26.671111</v>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1103">
+        <v>4</v>
+      </c>
+      <c r="K1103">
+        <v>6.667778</v>
+      </c>
+      <c r="L1103">
+        <v>6.667778</v>
+      </c>
+      <c r="M1103" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1103" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1103" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1103" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345051,"reliability":0.9651081,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1104">
+        <v>29.339259</v>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1104">
+        <v>4</v>
+      </c>
+      <c r="K1104">
+        <v>7.334815</v>
+      </c>
+      <c r="L1104">
+        <v>7.334815</v>
+      </c>
+      <c r="M1104" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1104" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1104" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1104" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9756727,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1105">
+        <v>37.337778</v>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1105">
+        <v>4</v>
+      </c>
+      <c r="K1105">
+        <v>9.334444</v>
+      </c>
+      <c r="L1105">
+        <v>9.334444</v>
+      </c>
+      <c r="M1105" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1105" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1105" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1105" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9871163,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1106">
+        <v>53.335556</v>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1106">
+        <v>8</v>
+      </c>
+      <c r="K1106">
+        <v>6.666944</v>
+      </c>
+      <c r="L1106">
+        <v>6.666944</v>
+      </c>
+      <c r="M1106" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1106" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1106" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1106" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9461276,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1107">
+        <v>56.005926</v>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1107">
+        <v>8</v>
+      </c>
+      <c r="K1107">
+        <v>7.000741</v>
+      </c>
+      <c r="L1107">
+        <v>7.000741</v>
+      </c>
+      <c r="M1107" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1107" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1107" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1107" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9660938,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1108">
+        <v>58.672593</v>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1108">
+        <v>8</v>
+      </c>
+      <c r="K1108">
+        <v>7.334074</v>
+      </c>
+      <c r="L1108">
+        <v>7.334074</v>
+      </c>
+      <c r="M1108" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1108" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1108" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1108" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9467472,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>20260601T095959Z</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>2026-06-01T10:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1109">
+        <v>64.002222</v>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1109">
+        <v>8</v>
+      </c>
+      <c r="K1109">
+        <v>8.000278</v>
+      </c>
+      <c r="L1109">
+        <v>8.000278</v>
+      </c>
+      <c r="M1109" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1109" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1109" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1109" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9630974,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1110">
+        <v>6.671111</v>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1110">
+        <v>1</v>
+      </c>
+      <c r="K1110">
+        <v>6.671111</v>
+      </c>
+      <c r="L1110">
+        <v>6.671111</v>
+      </c>
+      <c r="M1110" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1110" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1110" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1110" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345039,"reliability":0.9656431,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1111">
+        <v>6.671111</v>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1111">
+        <v>1</v>
+      </c>
+      <c r="K1111">
+        <v>6.671111</v>
+      </c>
+      <c r="L1111">
+        <v>6.671111</v>
+      </c>
+      <c r="M1111" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1111" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1111" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1111" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860229,"reliability":0.9835847,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1112">
+        <v>7.339259</v>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1112">
+        <v>1</v>
+      </c>
+      <c r="K1112">
+        <v>7.339259</v>
+      </c>
+      <c r="L1112">
+        <v>7.339259</v>
+      </c>
+      <c r="M1112" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1112" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1112" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1112" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9761355,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1113">
+        <v>13.337778</v>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1113">
+        <v>2</v>
+      </c>
+      <c r="K1113">
+        <v>6.668889</v>
+      </c>
+      <c r="L1113">
+        <v>6.668889</v>
+      </c>
+      <c r="M1113" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1113" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1113" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1113" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860225,"reliability":0.9835847,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1114">
+        <v>14.672593</v>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1114">
+        <v>2</v>
+      </c>
+      <c r="K1114">
+        <v>7.336296</v>
+      </c>
+      <c r="L1114">
+        <v>7.336296</v>
+      </c>
+      <c r="M1114" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1114" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1114" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1114" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9761355,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1115">
+        <v>18.671111</v>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1115">
+        <v>2</v>
+      </c>
+      <c r="K1115">
+        <v>9.335556</v>
+      </c>
+      <c r="L1115">
+        <v>9.335556</v>
+      </c>
+      <c r="M1115" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1115" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1115" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1115" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9873262,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1116">
+        <v>26.668889</v>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1116">
+        <v>4</v>
+      </c>
+      <c r="K1116">
+        <v>6.667222</v>
+      </c>
+      <c r="L1116">
+        <v>6.667222</v>
+      </c>
+      <c r="M1116" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1116" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1116" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1116" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.9467082,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1117">
+        <v>26.671111</v>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1117">
+        <v>4</v>
+      </c>
+      <c r="K1117">
+        <v>6.667778</v>
+      </c>
+      <c r="L1117">
+        <v>6.667778</v>
+      </c>
+      <c r="M1117" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1117" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1117" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1117" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9835847,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1118">
+        <v>28.215556</v>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1118">
+        <v>4</v>
+      </c>
+      <c r="K1118">
+        <v>7.053889</v>
+      </c>
+      <c r="L1118">
+        <v>7.053889</v>
+      </c>
+      <c r="M1118" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1118" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1118" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1118" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345032,"reliability":0.9705792,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1119">
+        <v>29.339259</v>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1119">
+        <v>4</v>
+      </c>
+      <c r="K1119">
+        <v>7.334815</v>
+      </c>
+      <c r="L1119">
+        <v>7.334815</v>
+      </c>
+      <c r="M1119" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1119" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1119" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1119" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9761355,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1120">
+        <v>53.335556</v>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1120">
+        <v>8</v>
+      </c>
+      <c r="K1120">
+        <v>6.666944</v>
+      </c>
+      <c r="L1120">
+        <v>6.666944</v>
+      </c>
+      <c r="M1120" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1120" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1120" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1120" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9467082,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1121">
+        <v>56.005926</v>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1121">
+        <v>8</v>
+      </c>
+      <c r="K1121">
+        <v>7.000741</v>
+      </c>
+      <c r="L1121">
+        <v>7.000741</v>
+      </c>
+      <c r="M1121" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1121" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1121" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1121" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.966133,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1122">
+        <v>58.672593</v>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1122">
+        <v>8</v>
+      </c>
+      <c r="K1122">
+        <v>7.334074</v>
+      </c>
+      <c r="L1122">
+        <v>7.334074</v>
+      </c>
+      <c r="M1122" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1122" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1122" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1122" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9473202,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>20260601T111616Z</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:16:19Z</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1123">
+        <v>64.002222</v>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1123">
+        <v>8</v>
+      </c>
+      <c r="K1123">
+        <v>8.000278</v>
+      </c>
+      <c r="L1123">
+        <v>8.000278</v>
+      </c>
+      <c r="M1123" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1123" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1123" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1123" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9631772,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1124">
+        <v>6.735556</v>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1124">
+        <v>1</v>
+      </c>
+      <c r="K1124">
+        <v>6.735556</v>
+      </c>
+      <c r="L1124">
+        <v>6.735556</v>
+      </c>
+      <c r="M1124" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1124" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1124" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1124" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860224,"reliability":0.9837102,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1125">
+        <v>7.055556</v>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1125">
+        <v>1</v>
+      </c>
+      <c r="K1125">
+        <v>7.055556</v>
+      </c>
+      <c r="L1125">
+        <v>7.055556</v>
+      </c>
+      <c r="M1125" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1125" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1125" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1125" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345031,"reliability":0.9709371,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1126">
+        <v>7.339259</v>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1126">
+        <v>1</v>
+      </c>
+      <c r="K1126">
+        <v>7.339259</v>
+      </c>
+      <c r="L1126">
+        <v>7.339259</v>
+      </c>
+      <c r="M1126" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1126" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1126" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1126" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404972,"reliability":0.9763604,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1127">
+        <v>13.468889</v>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1127">
+        <v>2</v>
+      </c>
+      <c r="K1127">
+        <v>6.734444</v>
+      </c>
+      <c r="L1127">
+        <v>6.734444</v>
+      </c>
+      <c r="M1127" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1127" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1127" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1127" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860221,"reliability":0.9837102,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1128">
+        <v>14.672593</v>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1128">
+        <v>2</v>
+      </c>
+      <c r="K1128">
+        <v>7.336296</v>
+      </c>
+      <c r="L1128">
+        <v>7.336296</v>
+      </c>
+      <c r="M1128" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1128" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1128" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1128" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.9763604,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1129">
+        <v>18.671111</v>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1129">
+        <v>2</v>
+      </c>
+      <c r="K1129">
+        <v>9.335556</v>
+      </c>
+      <c r="L1129">
+        <v>9.335556</v>
+      </c>
+      <c r="M1129" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1129" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1129" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1129" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430318,"reliability":0.9874087,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1130">
+        <v>26.668889</v>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1130">
+        <v>4</v>
+      </c>
+      <c r="K1130">
+        <v>6.667222</v>
+      </c>
+      <c r="L1130">
+        <v>6.667222</v>
+      </c>
+      <c r="M1130" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1130" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1130" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1130" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9469889,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1131">
+        <v>28.215556</v>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1131">
+        <v>4</v>
+      </c>
+      <c r="K1131">
+        <v>7.053889</v>
+      </c>
+      <c r="L1131">
+        <v>7.053889</v>
+      </c>
+      <c r="M1131" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1131" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1131" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1131" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345032,"reliability":0.9709371,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1132">
+        <v>29.339259</v>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1132">
+        <v>4</v>
+      </c>
+      <c r="K1132">
+        <v>7.334815</v>
+      </c>
+      <c r="L1132">
+        <v>7.334815</v>
+      </c>
+      <c r="M1132" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1132" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1132" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1132" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9763604,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1133">
+        <v>53.335556</v>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1133">
+        <v>8</v>
+      </c>
+      <c r="K1133">
+        <v>6.666944</v>
+      </c>
+      <c r="L1133">
+        <v>6.666944</v>
+      </c>
+      <c r="M1133" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1133" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1133" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1133" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9469889,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1134">
+        <v>56.005926</v>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1134">
+        <v>8</v>
+      </c>
+      <c r="K1134">
+        <v>7.000741</v>
+      </c>
+      <c r="L1134">
+        <v>7.000741</v>
+      </c>
+      <c r="M1134" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1134" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1134" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1134" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9661512,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1135">
+        <v>58.672593</v>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1135">
+        <v>8</v>
+      </c>
+      <c r="K1135">
+        <v>7.334074</v>
+      </c>
+      <c r="L1135">
+        <v>7.334074</v>
+      </c>
+      <c r="M1135" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1135" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1135" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1135" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9476058,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>20260601T124618Z</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>2026-06-01T12:46:20Z</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1136">
+        <v>64.002222</v>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1136">
+        <v>8</v>
+      </c>
+      <c r="K1136">
+        <v>8.000278</v>
+      </c>
+      <c r="L1136">
+        <v>8.000278</v>
+      </c>
+      <c r="M1136" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1136" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1136" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1136" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9632179,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/h100price/static/exports/b300_rental_prices.xlsx
+++ b/h100price/static/exports/b300_rental_prices.xlsx
@@ -84082,6 +84082,4964 @@
         </is>
       </c>
     </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1137">
+        <v>6.735556</v>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1137">
+        <v>1</v>
+      </c>
+      <c r="K1137">
+        <v>6.735556</v>
+      </c>
+      <c r="L1137">
+        <v>6.735556</v>
+      </c>
+      <c r="M1137" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1137" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1137" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1137" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860222,"reliability":0.9837102,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1138">
+        <v>7.055556</v>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1138">
+        <v>1</v>
+      </c>
+      <c r="K1138">
+        <v>7.055556</v>
+      </c>
+      <c r="L1138">
+        <v>7.055556</v>
+      </c>
+      <c r="M1138" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1138" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1138" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1138" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345028,"reliability":0.9709371,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1139">
+        <v>7.339259</v>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1139">
+        <v>1</v>
+      </c>
+      <c r="K1139">
+        <v>7.339259</v>
+      </c>
+      <c r="L1139">
+        <v>7.339259</v>
+      </c>
+      <c r="M1139" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1139" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1139" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1139" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404969,"reliability":0.9763604,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1140">
+        <v>13.468889</v>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1140">
+        <v>2</v>
+      </c>
+      <c r="K1140">
+        <v>6.734444</v>
+      </c>
+      <c r="L1140">
+        <v>6.734444</v>
+      </c>
+      <c r="M1140" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1140" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1140" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1140" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860221,"reliability":0.9837102,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1141">
+        <v>14.108889</v>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1141">
+        <v>2</v>
+      </c>
+      <c r="K1141">
+        <v>7.054444</v>
+      </c>
+      <c r="L1141">
+        <v>7.054444</v>
+      </c>
+      <c r="M1141" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1141" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1141" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1141" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9709371,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1142">
+        <v>14.672593</v>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1142">
+        <v>2</v>
+      </c>
+      <c r="K1142">
+        <v>7.336296</v>
+      </c>
+      <c r="L1142">
+        <v>7.336296</v>
+      </c>
+      <c r="M1142" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1142" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1142" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1142" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.9763604,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1143">
+        <v>26.668889</v>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1143">
+        <v>4</v>
+      </c>
+      <c r="K1143">
+        <v>6.667222</v>
+      </c>
+      <c r="L1143">
+        <v>6.667222</v>
+      </c>
+      <c r="M1143" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1143" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1143" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1143" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.9469889,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1144">
+        <v>26.935556</v>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1144">
+        <v>4</v>
+      </c>
+      <c r="K1144">
+        <v>6.733889</v>
+      </c>
+      <c r="L1144">
+        <v>6.733889</v>
+      </c>
+      <c r="M1144" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1144" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1144" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1144" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.9837102,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1145">
+        <v>29.339259</v>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1145">
+        <v>4</v>
+      </c>
+      <c r="K1145">
+        <v>7.334815</v>
+      </c>
+      <c r="L1145">
+        <v>7.334815</v>
+      </c>
+      <c r="M1145" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1145" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1145" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1145" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9763604,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1146">
+        <v>37.337778</v>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1146">
+        <v>4</v>
+      </c>
+      <c r="K1146">
+        <v>9.334444</v>
+      </c>
+      <c r="L1146">
+        <v>9.334444</v>
+      </c>
+      <c r="M1146" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1146" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1146" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1146" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9874087,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1147">
+        <v>53.335556</v>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1147">
+        <v>8</v>
+      </c>
+      <c r="K1147">
+        <v>6.666944</v>
+      </c>
+      <c r="L1147">
+        <v>6.666944</v>
+      </c>
+      <c r="M1147" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1147" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1147" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1147" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9469889,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1148">
+        <v>58.672593</v>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1148">
+        <v>8</v>
+      </c>
+      <c r="K1148">
+        <v>7.334074</v>
+      </c>
+      <c r="L1148">
+        <v>7.334074</v>
+      </c>
+      <c r="M1148" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1148" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1148" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1148" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9476058,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1149">
+        <v>61.339259</v>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1149">
+        <v>8</v>
+      </c>
+      <c r="K1149">
+        <v>7.667407</v>
+      </c>
+      <c r="L1149">
+        <v>7.667407</v>
+      </c>
+      <c r="M1149" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1149" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1149" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1149" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.966167,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>20260601T125959Z</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:00:08Z</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1150">
+        <v>64.002222</v>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1150">
+        <v>8</v>
+      </c>
+      <c r="K1150">
+        <v>8.000278</v>
+      </c>
+      <c r="L1150">
+        <v>8.000278</v>
+      </c>
+      <c r="M1150" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1150" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1150" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1150" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9632179,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1151">
+        <v>6.935556</v>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1151">
+        <v>1</v>
+      </c>
+      <c r="K1151">
+        <v>6.935556</v>
+      </c>
+      <c r="L1151">
+        <v>6.935556</v>
+      </c>
+      <c r="M1151" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1151" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1151" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1151" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860222,"reliability":0.9838586,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1152">
+        <v>7.055556</v>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1152">
+        <v>1</v>
+      </c>
+      <c r="K1152">
+        <v>7.055556</v>
+      </c>
+      <c r="L1152">
+        <v>7.055556</v>
+      </c>
+      <c r="M1152" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1152" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1152" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1152" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345034,"reliability":0.9713282,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1153">
+        <v>7.339259</v>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1153">
+        <v>1</v>
+      </c>
+      <c r="K1153">
+        <v>7.339259</v>
+      </c>
+      <c r="L1153">
+        <v>7.339259</v>
+      </c>
+      <c r="M1153" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1153" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1153" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1153" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404969,"reliability":0.9766111,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1154">
+        <v>13.868889</v>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1154">
+        <v>2</v>
+      </c>
+      <c r="K1154">
+        <v>6.934444</v>
+      </c>
+      <c r="L1154">
+        <v>6.934444</v>
+      </c>
+      <c r="M1154" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1154" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1154" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1154" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860220,"reliability":0.9838586,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1155">
+        <v>14.672593</v>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1155">
+        <v>2</v>
+      </c>
+      <c r="K1155">
+        <v>7.336296</v>
+      </c>
+      <c r="L1155">
+        <v>7.336296</v>
+      </c>
+      <c r="M1155" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1155" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1155" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1155" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.9766111,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1156">
+        <v>18.671111</v>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1156">
+        <v>2</v>
+      </c>
+      <c r="K1156">
+        <v>9.335556</v>
+      </c>
+      <c r="L1156">
+        <v>9.335556</v>
+      </c>
+      <c r="M1156" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1156" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1156" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1156" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430318,"reliability":0.9874887,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1157">
+        <v>26.668889</v>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1157">
+        <v>4</v>
+      </c>
+      <c r="K1157">
+        <v>6.667222</v>
+      </c>
+      <c r="L1157">
+        <v>6.667222</v>
+      </c>
+      <c r="M1157" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1157" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1157" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1157" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.94728,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1158">
+        <v>29.339259</v>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1158">
+        <v>4</v>
+      </c>
+      <c r="K1158">
+        <v>7.334815</v>
+      </c>
+      <c r="L1158">
+        <v>7.334815</v>
+      </c>
+      <c r="M1158" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1158" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1158" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1158" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9766111,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1159">
+        <v>37.337778</v>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1159">
+        <v>4</v>
+      </c>
+      <c r="K1159">
+        <v>9.334444</v>
+      </c>
+      <c r="L1159">
+        <v>9.334444</v>
+      </c>
+      <c r="M1159" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1159" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1159" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1159" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430317,"reliability":0.9874887,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1160">
+        <v>53.335556</v>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1160">
+        <v>8</v>
+      </c>
+      <c r="K1160">
+        <v>6.666944</v>
+      </c>
+      <c r="L1160">
+        <v>6.666944</v>
+      </c>
+      <c r="M1160" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1160" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1160" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1160" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.94728,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1161">
+        <v>58.672593</v>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1161">
+        <v>8</v>
+      </c>
+      <c r="K1161">
+        <v>7.334074</v>
+      </c>
+      <c r="L1161">
+        <v>7.334074</v>
+      </c>
+      <c r="M1161" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1161" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1161" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1161" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9479016,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1162">
+        <v>58.672593</v>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1162">
+        <v>8</v>
+      </c>
+      <c r="K1162">
+        <v>7.334074</v>
+      </c>
+      <c r="L1162">
+        <v>7.334074</v>
+      </c>
+      <c r="M1162" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1162" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1162" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1162" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9661743,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1163">
+        <v>64.002222</v>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1163">
+        <v>8</v>
+      </c>
+      <c r="K1163">
+        <v>8.000278</v>
+      </c>
+      <c r="L1163">
+        <v>8.000278</v>
+      </c>
+      <c r="M1163" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1163" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1163" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1163" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9632597,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>20260601T141649Z</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:16:50Z</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1164">
+        <v>74.671111</v>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1164">
+        <v>8</v>
+      </c>
+      <c r="K1164">
+        <v>9.333889</v>
+      </c>
+      <c r="L1164">
+        <v>9.333889</v>
+      </c>
+      <c r="M1164" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1164" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1164" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1164" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430322,"reliability":0.9874887,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1165">
+        <v>7.002222</v>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1165">
+        <v>1</v>
+      </c>
+      <c r="K1165">
+        <v>7.002222</v>
+      </c>
+      <c r="L1165">
+        <v>7.002222</v>
+      </c>
+      <c r="M1165" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1165" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1165" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1165" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860223,"reliability":0.9839059,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1166">
+        <v>7.055556</v>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1166">
+        <v>1</v>
+      </c>
+      <c r="K1166">
+        <v>7.055556</v>
+      </c>
+      <c r="L1166">
+        <v>7.055556</v>
+      </c>
+      <c r="M1166" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1166" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1166" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1166" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345034,"reliability":0.9717129,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1167">
+        <v>7.339259</v>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1167">
+        <v>1</v>
+      </c>
+      <c r="K1167">
+        <v>7.339259</v>
+      </c>
+      <c r="L1167">
+        <v>7.339259</v>
+      </c>
+      <c r="M1167" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1167" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1167" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1167" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404972,"reliability":0.9768652,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1168">
+        <v>13.975556</v>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1168">
+        <v>2</v>
+      </c>
+      <c r="K1168">
+        <v>6.987778</v>
+      </c>
+      <c r="L1168">
+        <v>6.987778</v>
+      </c>
+      <c r="M1168" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1168" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1168" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1168" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9875785,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1169">
+        <v>14.002222</v>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1169">
+        <v>2</v>
+      </c>
+      <c r="K1169">
+        <v>7.001111</v>
+      </c>
+      <c r="L1169">
+        <v>7.001111</v>
+      </c>
+      <c r="M1169" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1169" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1169" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1169" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860220,"reliability":0.9839059,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1170">
+        <v>14.672593</v>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1170">
+        <v>2</v>
+      </c>
+      <c r="K1170">
+        <v>7.336296</v>
+      </c>
+      <c r="L1170">
+        <v>7.336296</v>
+      </c>
+      <c r="M1170" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1170" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1170" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1170" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.9768652,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1171">
+        <v>26.668889</v>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1171">
+        <v>4</v>
+      </c>
+      <c r="K1171">
+        <v>6.667222</v>
+      </c>
+      <c r="L1171">
+        <v>6.667222</v>
+      </c>
+      <c r="M1171" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1171" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1171" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1171" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9475646,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1172">
+        <v>27.948889</v>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1172">
+        <v>4</v>
+      </c>
+      <c r="K1172">
+        <v>6.987222</v>
+      </c>
+      <c r="L1172">
+        <v>6.987222</v>
+      </c>
+      <c r="M1172" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1172" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1172" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1172" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430321,"reliability":0.9875785,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1173">
+        <v>29.339259</v>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1173">
+        <v>4</v>
+      </c>
+      <c r="K1173">
+        <v>7.334815</v>
+      </c>
+      <c r="L1173">
+        <v>7.334815</v>
+      </c>
+      <c r="M1173" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1173" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1173" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1173" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9768652,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1174">
+        <v>53.335556</v>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1174">
+        <v>8</v>
+      </c>
+      <c r="K1174">
+        <v>6.666944</v>
+      </c>
+      <c r="L1174">
+        <v>6.666944</v>
+      </c>
+      <c r="M1174" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1174" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1174" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1174" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9475646,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1175">
+        <v>55.895556</v>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1175">
+        <v>8</v>
+      </c>
+      <c r="K1175">
+        <v>6.986944</v>
+      </c>
+      <c r="L1175">
+        <v>6.986944</v>
+      </c>
+      <c r="M1175" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1175" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1175" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1175" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430322,"reliability":0.9875785,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1176">
+        <v>58.672593</v>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1176">
+        <v>8</v>
+      </c>
+      <c r="K1176">
+        <v>7.334074</v>
+      </c>
+      <c r="L1176">
+        <v>7.334074</v>
+      </c>
+      <c r="M1176" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1176" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1176" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1176" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9481744,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1177">
+        <v>58.672593</v>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1177">
+        <v>8</v>
+      </c>
+      <c r="K1177">
+        <v>7.334074</v>
+      </c>
+      <c r="L1177">
+        <v>7.334074</v>
+      </c>
+      <c r="M1177" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1177" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1177" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1177" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9661912,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>20260601T145959Z</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1178">
+        <v>64.002222</v>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1178">
+        <v>8</v>
+      </c>
+      <c r="K1178">
+        <v>8.000278</v>
+      </c>
+      <c r="L1178">
+        <v>8.000278</v>
+      </c>
+      <c r="M1178" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1178" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1178" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1178" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9633004,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1179">
+        <v>7.002222</v>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1179">
+        <v>1</v>
+      </c>
+      <c r="K1179">
+        <v>7.002222</v>
+      </c>
+      <c r="L1179">
+        <v>7.002222</v>
+      </c>
+      <c r="M1179" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1179" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1179" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1179" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860222,"reliability":0.9839475,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1180">
+        <v>7.055556</v>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1180">
+        <v>1</v>
+      </c>
+      <c r="K1180">
+        <v>7.055556</v>
+      </c>
+      <c r="L1180">
+        <v>7.055556</v>
+      </c>
+      <c r="M1180" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1180" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1180" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1180" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345029,"reliability":0.9720899,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G1181">
+        <v>7.339259</v>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1181">
+        <v>1</v>
+      </c>
+      <c r="K1181">
+        <v>7.339259</v>
+      </c>
+      <c r="L1181">
+        <v>7.339259</v>
+      </c>
+      <c r="M1181" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1181" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1181" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1181" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404972,"reliability":0.9771071,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1182">
+        <v>14.108889</v>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1182">
+        <v>2</v>
+      </c>
+      <c r="K1182">
+        <v>7.054444</v>
+      </c>
+      <c r="L1182">
+        <v>7.054444</v>
+      </c>
+      <c r="M1182" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1182" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1182" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1182" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9720899,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G1183">
+        <v>14.672593</v>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1183">
+        <v>2</v>
+      </c>
+      <c r="K1183">
+        <v>7.336296</v>
+      </c>
+      <c r="L1183">
+        <v>7.336296</v>
+      </c>
+      <c r="M1183" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1183" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1183" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1183" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.9771071,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1184">
+        <v>26.668889</v>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1184">
+        <v>4</v>
+      </c>
+      <c r="K1184">
+        <v>6.667222</v>
+      </c>
+      <c r="L1184">
+        <v>6.667222</v>
+      </c>
+      <c r="M1184" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1184" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1184" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1184" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.9478428,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1185">
+        <v>27.415556</v>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1185">
+        <v>4</v>
+      </c>
+      <c r="K1185">
+        <v>6.853889</v>
+      </c>
+      <c r="L1185">
+        <v>6.853889</v>
+      </c>
+      <c r="M1185" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1185" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1185" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1185" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430321,"reliability":0.9876327,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G1186">
+        <v>29.339259</v>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1186">
+        <v>4</v>
+      </c>
+      <c r="K1186">
+        <v>7.334815</v>
+      </c>
+      <c r="L1186">
+        <v>7.334815</v>
+      </c>
+      <c r="M1186" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1186" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1186" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1186" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9771071,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1187">
+        <v>53.335556</v>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1187">
+        <v>8</v>
+      </c>
+      <c r="K1187">
+        <v>6.666944</v>
+      </c>
+      <c r="L1187">
+        <v>6.666944</v>
+      </c>
+      <c r="M1187" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1187" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1187" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1187" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9478428,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1188">
+        <v>54.828889</v>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1188">
+        <v>8</v>
+      </c>
+      <c r="K1188">
+        <v>6.853611</v>
+      </c>
+      <c r="L1188">
+        <v>6.853611</v>
+      </c>
+      <c r="M1188" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1188" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1188" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1188" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430322,"reliability":0.9876327,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1189">
+        <v>58.672593</v>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1189">
+        <v>8</v>
+      </c>
+      <c r="K1189">
+        <v>7.334074</v>
+      </c>
+      <c r="L1189">
+        <v>7.334074</v>
+      </c>
+      <c r="M1189" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1189" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1189" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1189" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652077,"reliability":0.9484473,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1190">
+        <v>58.672593</v>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1190">
+        <v>8</v>
+      </c>
+      <c r="K1190">
+        <v>7.334074</v>
+      </c>
+      <c r="L1190">
+        <v>7.334074</v>
+      </c>
+      <c r="M1190" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1190" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1190" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1190" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9662106,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>20260601T155959Z</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:00:11Z</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G1191">
+        <v>64.002222</v>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1191">
+        <v>8</v>
+      </c>
+      <c r="K1191">
+        <v>8.000278</v>
+      </c>
+      <c r="L1191">
+        <v>8.000278</v>
+      </c>
+      <c r="M1191" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1191" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1191" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1191" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9633416,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1192">
+        <v>7.068889</v>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1192">
+        <v>1</v>
+      </c>
+      <c r="K1192">
+        <v>7.068889</v>
+      </c>
+      <c r="L1192">
+        <v>7.068889</v>
+      </c>
+      <c r="M1192" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1192" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1192" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1192" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345031,"reliability":0.9738014,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1193">
+        <v>7.068889</v>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1193">
+        <v>1</v>
+      </c>
+      <c r="K1193">
+        <v>7.068889</v>
+      </c>
+      <c r="L1193">
+        <v>7.068889</v>
+      </c>
+      <c r="M1193" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1193" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1193" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1193" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860222,"reliability":0.984372,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1194">
+        <v>7.339259</v>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1194">
+        <v>1</v>
+      </c>
+      <c r="K1194">
+        <v>7.339259</v>
+      </c>
+      <c r="L1194">
+        <v>7.339259</v>
+      </c>
+      <c r="M1194" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1194" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1194" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1194" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404967,"reliability":0.978189,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1195">
+        <v>14.135556</v>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1195">
+        <v>2</v>
+      </c>
+      <c r="K1195">
+        <v>7.067778</v>
+      </c>
+      <c r="L1195">
+        <v>7.067778</v>
+      </c>
+      <c r="M1195" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1195" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1195" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1195" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345026,"reliability":0.9738014,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1196">
+        <v>14.135556</v>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1196">
+        <v>2</v>
+      </c>
+      <c r="K1196">
+        <v>7.067778</v>
+      </c>
+      <c r="L1196">
+        <v>7.067778</v>
+      </c>
+      <c r="M1196" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1196" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1196" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1196" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860216,"reliability":0.984372,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1197">
+        <v>14.672593</v>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1197">
+        <v>2</v>
+      </c>
+      <c r="K1197">
+        <v>7.336296</v>
+      </c>
+      <c r="L1197">
+        <v>7.336296</v>
+      </c>
+      <c r="M1197" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1197" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1197" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1197" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.978189,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1198">
+        <v>26.668889</v>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1198">
+        <v>4</v>
+      </c>
+      <c r="K1198">
+        <v>6.667222</v>
+      </c>
+      <c r="L1198">
+        <v>6.667222</v>
+      </c>
+      <c r="M1198" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1198" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1198" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1198" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.949098,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1199">
+        <v>28.268889</v>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1199">
+        <v>4</v>
+      </c>
+      <c r="K1199">
+        <v>7.067222</v>
+      </c>
+      <c r="L1199">
+        <v>7.067222</v>
+      </c>
+      <c r="M1199" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1199" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1199" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1199" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345032,"reliability":0.9738014,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1200">
+        <v>29.339259</v>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1200">
+        <v>4</v>
+      </c>
+      <c r="K1200">
+        <v>7.334815</v>
+      </c>
+      <c r="L1200">
+        <v>7.334815</v>
+      </c>
+      <c r="M1200" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1200" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1200" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1200" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.978189,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1201">
+        <v>53.335556</v>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1201">
+        <v>8</v>
+      </c>
+      <c r="K1201">
+        <v>6.666944</v>
+      </c>
+      <c r="L1201">
+        <v>6.666944</v>
+      </c>
+      <c r="M1201" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1201" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1201" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1201" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.949098,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1202">
+        <v>61.339259</v>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1202">
+        <v>8</v>
+      </c>
+      <c r="K1202">
+        <v>7.667407</v>
+      </c>
+      <c r="L1202">
+        <v>7.667407</v>
+      </c>
+      <c r="M1202" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1202" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1202" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1202" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9663035,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>20260601T203304Z</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:33:08Z</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1203">
+        <v>64.002222</v>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1203">
+        <v>8</v>
+      </c>
+      <c r="K1203">
+        <v>8.000278</v>
+      </c>
+      <c r="L1203">
+        <v>8.000278</v>
+      </c>
+      <c r="M1203" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1203" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1203" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1203" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.963533,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/h100price/static/exports/b300_rental_prices.xlsx
+++ b/h100price/static/exports/b300_rental_prices.xlsx
@@ -89040,6 +89040,4076 @@
         </is>
       </c>
     </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1204">
+        <v>7.068889</v>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1204">
+        <v>1</v>
+      </c>
+      <c r="K1204">
+        <v>7.068889</v>
+      </c>
+      <c r="L1204">
+        <v>7.068889</v>
+      </c>
+      <c r="M1204" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1204" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1204" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1204" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345034,"reliability":0.9738014,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1205">
+        <v>7.068889</v>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1205">
+        <v>1</v>
+      </c>
+      <c r="K1205">
+        <v>7.068889</v>
+      </c>
+      <c r="L1205">
+        <v>7.068889</v>
+      </c>
+      <c r="M1205" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1205" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1205" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1205" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860229,"reliability":0.984372,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1206">
+        <v>7.339259</v>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1206">
+        <v>1</v>
+      </c>
+      <c r="K1206">
+        <v>7.339259</v>
+      </c>
+      <c r="L1206">
+        <v>7.339259</v>
+      </c>
+      <c r="M1206" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1206" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1206" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1206" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404969,"reliability":0.978189,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1207">
+        <v>14.135556</v>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1207">
+        <v>2</v>
+      </c>
+      <c r="K1207">
+        <v>7.067778</v>
+      </c>
+      <c r="L1207">
+        <v>7.067778</v>
+      </c>
+      <c r="M1207" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1207" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1207" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1207" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9738014,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1208">
+        <v>14.135556</v>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1208">
+        <v>2</v>
+      </c>
+      <c r="K1208">
+        <v>7.067778</v>
+      </c>
+      <c r="L1208">
+        <v>7.067778</v>
+      </c>
+      <c r="M1208" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1208" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1208" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1208" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860216,"reliability":0.984372,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1209">
+        <v>14.672593</v>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1209">
+        <v>2</v>
+      </c>
+      <c r="K1209">
+        <v>7.336296</v>
+      </c>
+      <c r="L1209">
+        <v>7.336296</v>
+      </c>
+      <c r="M1209" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1209" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1209" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1209" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.978189,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1210">
+        <v>26.668889</v>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1210">
+        <v>4</v>
+      </c>
+      <c r="K1210">
+        <v>6.667222</v>
+      </c>
+      <c r="L1210">
+        <v>6.667222</v>
+      </c>
+      <c r="M1210" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1210" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1210" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1210" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.949098,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1211">
+        <v>28.268889</v>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1211">
+        <v>4</v>
+      </c>
+      <c r="K1211">
+        <v>7.067222</v>
+      </c>
+      <c r="L1211">
+        <v>7.067222</v>
+      </c>
+      <c r="M1211" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1211" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1211" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1211" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860227,"reliability":0.984372,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1212">
+        <v>28.268889</v>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1212">
+        <v>4</v>
+      </c>
+      <c r="K1212">
+        <v>7.067222</v>
+      </c>
+      <c r="L1212">
+        <v>7.067222</v>
+      </c>
+      <c r="M1212" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1212" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1212" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1212" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345032,"reliability":0.9738014,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1213">
+        <v>29.339259</v>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1213">
+        <v>4</v>
+      </c>
+      <c r="K1213">
+        <v>7.334815</v>
+      </c>
+      <c r="L1213">
+        <v>7.334815</v>
+      </c>
+      <c r="M1213" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1213" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1213" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1213" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.978189,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1214">
+        <v>53.335556</v>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1214">
+        <v>8</v>
+      </c>
+      <c r="K1214">
+        <v>6.666944</v>
+      </c>
+      <c r="L1214">
+        <v>6.666944</v>
+      </c>
+      <c r="M1214" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1214" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1214" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1214" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.949098,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1215">
+        <v>61.339259</v>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1215">
+        <v>8</v>
+      </c>
+      <c r="K1215">
+        <v>7.667407</v>
+      </c>
+      <c r="L1215">
+        <v>7.667407</v>
+      </c>
+      <c r="M1215" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1215" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1215" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1215" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9663035,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>20260601T210143Z</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:01:47Z</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1216">
+        <v>64.002222</v>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1216">
+        <v>8</v>
+      </c>
+      <c r="K1216">
+        <v>8.000278</v>
+      </c>
+      <c r="L1216">
+        <v>8.000278</v>
+      </c>
+      <c r="M1216" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1216" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1216" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1216" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.963533,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1217">
+        <v>7.339259</v>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1217">
+        <v>1</v>
+      </c>
+      <c r="K1217">
+        <v>7.339259</v>
+      </c>
+      <c r="L1217">
+        <v>7.339259</v>
+      </c>
+      <c r="M1217" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1217" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1217" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1217" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404967,"reliability":0.9789768,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1218">
+        <v>8.015556</v>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1218">
+        <v>1</v>
+      </c>
+      <c r="K1218">
+        <v>8.015556</v>
+      </c>
+      <c r="L1218">
+        <v>8.015556</v>
+      </c>
+      <c r="M1218" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1218" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1218" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1218" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345022,"reliability":0.9748683,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1219">
+        <v>8.082222</v>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1219">
+        <v>1</v>
+      </c>
+      <c r="K1219">
+        <v>8.082222</v>
+      </c>
+      <c r="L1219">
+        <v>8.082222</v>
+      </c>
+      <c r="M1219" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1219" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1219" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1219" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860224,"reliability":0.9846948,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1220">
+        <v>14.672593</v>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1220">
+        <v>2</v>
+      </c>
+      <c r="K1220">
+        <v>7.336296</v>
+      </c>
+      <c r="L1220">
+        <v>7.336296</v>
+      </c>
+      <c r="M1220" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1220" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1220" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1220" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9789768,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1221">
+        <v>16.028889</v>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1221">
+        <v>2</v>
+      </c>
+      <c r="K1221">
+        <v>8.014444</v>
+      </c>
+      <c r="L1221">
+        <v>8.014444</v>
+      </c>
+      <c r="M1221" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1221" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1221" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1221" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9748683,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1222">
+        <v>16.162222</v>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1222">
+        <v>2</v>
+      </c>
+      <c r="K1222">
+        <v>8.081111</v>
+      </c>
+      <c r="L1222">
+        <v>8.081111</v>
+      </c>
+      <c r="M1222" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1222" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1222" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1222" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860216,"reliability":0.9846948,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1223">
+        <v>26.668889</v>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1223">
+        <v>4</v>
+      </c>
+      <c r="K1223">
+        <v>6.667222</v>
+      </c>
+      <c r="L1223">
+        <v>6.667222</v>
+      </c>
+      <c r="M1223" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1223" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1223" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1223" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9500298,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1224">
+        <v>32.055556</v>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1224">
+        <v>4</v>
+      </c>
+      <c r="K1224">
+        <v>8.013889</v>
+      </c>
+      <c r="L1224">
+        <v>8.013889</v>
+      </c>
+      <c r="M1224" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1224" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1224" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1224" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345023,"reliability":0.9748683,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1225">
+        <v>53.335556</v>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1225">
+        <v>8</v>
+      </c>
+      <c r="K1225">
+        <v>6.666944</v>
+      </c>
+      <c r="L1225">
+        <v>6.666944</v>
+      </c>
+      <c r="M1225" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1225" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1225" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1225" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9500298,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1226">
+        <v>64.002222</v>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1226">
+        <v>8</v>
+      </c>
+      <c r="K1226">
+        <v>8.000278</v>
+      </c>
+      <c r="L1226">
+        <v>8.000278</v>
+      </c>
+      <c r="M1226" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1226" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1226" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1226" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9636855,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1227">
+        <v>64.005926</v>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1227">
+        <v>8</v>
+      </c>
+      <c r="K1227">
+        <v>8.000741</v>
+      </c>
+      <c r="L1227">
+        <v>8.000741</v>
+      </c>
+      <c r="M1227" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1227" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1227" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1227" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652137,"reliability":0.9400768,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1228">
+        <v>64.005926</v>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1228">
+        <v>8</v>
+      </c>
+      <c r="K1228">
+        <v>8.000741</v>
+      </c>
+      <c r="L1228">
+        <v>8.000741</v>
+      </c>
+      <c r="M1228" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1228" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1228" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1228" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38624426,"reliability":0.94613,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>20260602T005627Z</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:56:29Z</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1229">
+        <v>64.108889</v>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1229">
+        <v>8</v>
+      </c>
+      <c r="K1229">
+        <v>8.013611</v>
+      </c>
+      <c r="L1229">
+        <v>8.013611</v>
+      </c>
+      <c r="M1229" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1229" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1229" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1229" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9748683,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1230">
+        <v>7.339259</v>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1230">
+        <v>1</v>
+      </c>
+      <c r="K1230">
+        <v>7.339259</v>
+      </c>
+      <c r="L1230">
+        <v>7.339259</v>
+      </c>
+      <c r="M1230" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1230" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1230" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1230" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404969,"reliability":0.9789768,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1231">
+        <v>8.015556</v>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1231">
+        <v>1</v>
+      </c>
+      <c r="K1231">
+        <v>8.015556</v>
+      </c>
+      <c r="L1231">
+        <v>8.015556</v>
+      </c>
+      <c r="M1231" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1231" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1231" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1231" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345024,"reliability":0.9748683,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1232">
+        <v>8.082222</v>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1232">
+        <v>1</v>
+      </c>
+      <c r="K1232">
+        <v>8.082222</v>
+      </c>
+      <c r="L1232">
+        <v>8.082222</v>
+      </c>
+      <c r="M1232" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1232" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1232" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1232" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860229,"reliability":0.9846948,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1233">
+        <v>14.672593</v>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1233">
+        <v>2</v>
+      </c>
+      <c r="K1233">
+        <v>7.336296</v>
+      </c>
+      <c r="L1233">
+        <v>7.336296</v>
+      </c>
+      <c r="M1233" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1233" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1233" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1233" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9789768,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1234">
+        <v>16.028889</v>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1234">
+        <v>2</v>
+      </c>
+      <c r="K1234">
+        <v>8.014444</v>
+      </c>
+      <c r="L1234">
+        <v>8.014444</v>
+      </c>
+      <c r="M1234" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1234" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1234" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1234" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345021,"reliability":0.9748683,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1235">
+        <v>16.162222</v>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1235">
+        <v>2</v>
+      </c>
+      <c r="K1235">
+        <v>8.081111</v>
+      </c>
+      <c r="L1235">
+        <v>8.081111</v>
+      </c>
+      <c r="M1235" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1235" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1235" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1235" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860216,"reliability":0.9846948,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1236">
+        <v>26.668889</v>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1236">
+        <v>4</v>
+      </c>
+      <c r="K1236">
+        <v>6.667222</v>
+      </c>
+      <c r="L1236">
+        <v>6.667222</v>
+      </c>
+      <c r="M1236" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1236" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1236" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1236" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.9500298,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1237">
+        <v>29.339259</v>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1237">
+        <v>4</v>
+      </c>
+      <c r="K1237">
+        <v>7.334815</v>
+      </c>
+      <c r="L1237">
+        <v>7.334815</v>
+      </c>
+      <c r="M1237" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1237" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1237" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1237" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404968,"reliability":0.9789768,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1238">
+        <v>32.055556</v>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1238">
+        <v>4</v>
+      </c>
+      <c r="K1238">
+        <v>8.013889</v>
+      </c>
+      <c r="L1238">
+        <v>8.013889</v>
+      </c>
+      <c r="M1238" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1238" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1238" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1238" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345032,"reliability":0.9748683,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1239">
+        <v>53.335556</v>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1239">
+        <v>8</v>
+      </c>
+      <c r="K1239">
+        <v>6.666944</v>
+      </c>
+      <c r="L1239">
+        <v>6.666944</v>
+      </c>
+      <c r="M1239" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1239" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1239" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1239" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9500298,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1240">
+        <v>64.002222</v>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1240">
+        <v>8</v>
+      </c>
+      <c r="K1240">
+        <v>8.000278</v>
+      </c>
+      <c r="L1240">
+        <v>8.000278</v>
+      </c>
+      <c r="M1240" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1240" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1240" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1240" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9636855,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1241">
+        <v>64.005926</v>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1241">
+        <v>8</v>
+      </c>
+      <c r="K1241">
+        <v>8.000741</v>
+      </c>
+      <c r="L1241">
+        <v>8.000741</v>
+      </c>
+      <c r="M1241" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1241" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1241" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1241" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38652137,"reliability":0.9400768,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1242">
+        <v>64.005926</v>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1242">
+        <v>8</v>
+      </c>
+      <c r="K1242">
+        <v>8.000741</v>
+      </c>
+      <c r="L1242">
+        <v>8.000741</v>
+      </c>
+      <c r="M1242" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1242" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1242" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1242" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38624426,"reliability":0.94613,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>20260602T005959Z</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:00:14Z</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1243">
+        <v>64.108889</v>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1243">
+        <v>8</v>
+      </c>
+      <c r="K1243">
+        <v>8.013611</v>
+      </c>
+      <c r="L1243">
+        <v>8.013611</v>
+      </c>
+      <c r="M1243" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1243" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1243" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1243" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9748683,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1244">
+        <v>6.668889</v>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1244">
+        <v>1</v>
+      </c>
+      <c r="K1244">
+        <v>6.668889</v>
+      </c>
+      <c r="L1244">
+        <v>6.668889</v>
+      </c>
+      <c r="M1244" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1244" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1244" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1244" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345020,"reliability":0.9775845,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1245">
+        <v>8.672593</v>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1245">
+        <v>1</v>
+      </c>
+      <c r="K1245">
+        <v>8.672593</v>
+      </c>
+      <c r="L1245">
+        <v>8.672593</v>
+      </c>
+      <c r="M1245" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1245" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1245" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1245" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404969,"reliability":0.9811214,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>B300 x1</t>
+        </is>
+      </c>
+      <c r="G1246">
+        <v>9.335556</v>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1246">
+        <v>1</v>
+      </c>
+      <c r="K1246">
+        <v>9.335556</v>
+      </c>
+      <c r="L1246">
+        <v>9.335556</v>
+      </c>
+      <c r="M1246" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1246" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1246" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1246" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860223,"reliability":0.9855813,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1247">
+        <v>13.335556</v>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1247">
+        <v>2</v>
+      </c>
+      <c r="K1247">
+        <v>6.667778</v>
+      </c>
+      <c r="L1247">
+        <v>6.667778</v>
+      </c>
+      <c r="M1247" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1247" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1247" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1247" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345025,"reliability":0.9775845,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1248">
+        <v>17.339259</v>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1248">
+        <v>2</v>
+      </c>
+      <c r="K1248">
+        <v>8.66963</v>
+      </c>
+      <c r="L1248">
+        <v>8.66963</v>
+      </c>
+      <c r="M1248" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1248" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1248" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1248" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404966,"reliability":0.9811214,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>B300 x2</t>
+        </is>
+      </c>
+      <c r="G1249">
+        <v>18.668889</v>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1249">
+        <v>2</v>
+      </c>
+      <c r="K1249">
+        <v>9.334444</v>
+      </c>
+      <c r="L1249">
+        <v>9.334444</v>
+      </c>
+      <c r="M1249" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1249" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1249" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1249" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860216,"reliability":0.9855813,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1250">
+        <v>25.335556</v>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1250">
+        <v>4</v>
+      </c>
+      <c r="K1250">
+        <v>6.333889</v>
+      </c>
+      <c r="L1250">
+        <v>6.333889</v>
+      </c>
+      <c r="M1250" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1250" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1250" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1250" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9527692,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1251">
+        <v>26.668889</v>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1251">
+        <v>4</v>
+      </c>
+      <c r="K1251">
+        <v>6.667222</v>
+      </c>
+      <c r="L1251">
+        <v>6.667222</v>
+      </c>
+      <c r="M1251" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1251" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1251" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1251" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345032,"reliability":0.9775845,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1252">
+        <v>33.339259</v>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1252">
+        <v>4</v>
+      </c>
+      <c r="K1252">
+        <v>8.334815</v>
+      </c>
+      <c r="L1252">
+        <v>8.334815</v>
+      </c>
+      <c r="M1252" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1252" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1252" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1252" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":39030617,"reliability":0.9637299,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1253">
+        <v>36.005926</v>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1253">
+        <v>4</v>
+      </c>
+      <c r="K1253">
+        <v>9.001481</v>
+      </c>
+      <c r="L1253">
+        <v>9.001481</v>
+      </c>
+      <c r="M1253" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1253" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1253" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1253" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":39030960,"reliability":0.948158,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>B300 x4</t>
+        </is>
+      </c>
+      <c r="G1254">
+        <v>37.335556</v>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1254">
+        <v>4</v>
+      </c>
+      <c r="K1254">
+        <v>9.333889</v>
+      </c>
+      <c r="L1254">
+        <v>9.333889</v>
+      </c>
+      <c r="M1254" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1254" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1254" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1254" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37860218,"reliability":0.9855813,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1255">
+        <v>50.668889</v>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1255">
+        <v>8</v>
+      </c>
+      <c r="K1255">
+        <v>6.333611</v>
+      </c>
+      <c r="L1255">
+        <v>6.333611</v>
+      </c>
+      <c r="M1255" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1255" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1255" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1255" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9527692,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1256">
+        <v>58.668889</v>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1256">
+        <v>8</v>
+      </c>
+      <c r="K1256">
+        <v>7.333611</v>
+      </c>
+      <c r="L1256">
+        <v>7.333611</v>
+      </c>
+      <c r="M1256" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1256" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1256" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1256" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9641719,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1257">
+        <v>66.672593</v>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1257">
+        <v>8</v>
+      </c>
+      <c r="K1257">
+        <v>8.334074</v>
+      </c>
+      <c r="L1257">
+        <v>8.334074</v>
+      </c>
+      <c r="M1257" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1257" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1257" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1257" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":39030615,"reliability":0.9637299,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>20260602T143722Z</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>2026-06-02T14:37:23Z</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>B300 x8</t>
+        </is>
+      </c>
+      <c r="G1258">
+        <v>72.005926</v>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1258">
+        <v>8</v>
+      </c>
+      <c r="K1258">
+        <v>9.000741</v>
+      </c>
+      <c r="L1258">
+        <v>9.000741</v>
+      </c>
+      <c r="M1258" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1258" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1258" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1258" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":39030961,"reliability":0.948158,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>